--- a/data/merged/2026-09-09/MERGED_UK_Spot-Cleaner_2026-09-09.xlsx
+++ b/data/merged/2026-09-09/MERGED_UK_Spot-Cleaner_2026-09-09.xlsx
@@ -5421,14 +5421,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5465,13 +5465,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5509,13 +5509,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5553,13 +5553,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5597,13 +5597,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5641,14 +5641,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5665,94 +5665,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId32" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="Product 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId33" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Product 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId34" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6094,7 +6006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -13797,40 +13709,40 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0FNX6YLCJ</t>
+          <t>B0FXGBT4LF</t>
         </is>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Domixo</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0FNX6YLCJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Domixo</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Shark StainForce Dual-Formula Refill Cartridge, 2 x 500ml XSKBDHXCM500UKsValue 2-Pack, Formulated to tackle tough stains an</t>
+          <t>Domixo Carpet Cleaner Machines, Hot Water Multi-Purpose Portable Spot Cleaner, Wet/dry Upholstery Cleaner, 450W &amp; Touchscreen</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FNX6YLCJ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FXGBT4LF?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71SuXoGPIQL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71NkpfFNvkL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0FNX6YLCJ</t>
+          <t>B0FXGBT4LF</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -13844,13 +13756,13 @@
         </is>
       </c>
       <c r="O34" s="15">
-        <v>1385</v>
+        <v>24972</v>
       </c>
       <c r="P34" s="15">
-        <v>4170</v>
+        <v>-359</v>
       </c>
       <c r="Q34" s="16">
-        <v>0.75</v>
+        <v>-0.01</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
@@ -13859,65 +13771,65 @@
       </c>
       <c r="S34" s="18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T34" s="15">
-        <v>904</v>
+        <v>214</v>
       </c>
       <c r="U34" s="16">
-        <v>-0.04</v>
+        <v>0.66</v>
       </c>
       <c r="V34" s="15">
-        <v>15061</v>
+        <v>14978</v>
       </c>
       <c r="W34" s="15" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X34" s="15">
-        <v>20704</v>
+        <v>6745</v>
       </c>
       <c r="Y34" s="19">
         <v>1</v>
       </c>
       <c r="Z34" s="20">
-        <v>19.99</v>
+        <v>69.99</v>
       </c>
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34" s="15"/>
       <c r="AD34" s="19">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="AE34" s="15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AF34" s="21">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AG34" s="22">
-        <v>0.0111</v>
+        <v>0.013999999999999999</v>
       </c>
       <c r="AH34" s="20">
-        <v>3.1</v>
+        <v>3.43</v>
       </c>
       <c r="AI34" s="16">
-        <v>0.81</v>
+        <v>0.95</v>
       </c>
       <c r="AJ34"/>
       <c r="AK34" s="13" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AL34" s="19">
-        <v>365</v>
+        <v>306</v>
       </c>
       <c r="AM34" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN34" s="13"/>
@@ -13927,21 +13839,33 @@
         <v>10</v>
       </c>
       <c r="AR34" s="19">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AS34" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>qingziyu58</t>
         </is>
       </c>
       <c r="AT34" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU34" s="13"/>
-      <c r="AV34" s="14"/>
-      <c r="AW34" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU34" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV34" s="14" t="inlineStr">
+        <is>
+          <t>广州市 广东 510080 CN</t>
+        </is>
+      </c>
+      <c r="AW34" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WYJ2QAIMP7S0</t>
+        </is>
+      </c>
       <c r="AX34" s="13"/>
       <c r="AY34" s="13" t="inlineStr">
         <is>
@@ -13972,47 +13896,47 @@
       </c>
       <c r="BJ34" s="23" t="inlineStr">
         <is>
-          <t>1.3 kg</t>
+          <t>4.61 kg</t>
         </is>
       </c>
       <c r="BK34" s="23" t="inlineStr">
         <is>
-          <t>1.30 kg</t>
+          <t>4.61 kg</t>
         </is>
       </c>
       <c r="BL34" s="23" t="inlineStr">
         <is>
-          <t>15.7 x 15.5 x 10.8 cm</t>
+          <t>19.4 x 33.4 x 44.4 cm</t>
         </is>
       </c>
       <c r="BM34" s="23" t="inlineStr">
         <is>
-          <t>15.70 x 15.50 x 10.80 cm</t>
+          <t>19.40 x 33.40 x 44.40 cm</t>
         </is>
       </c>
       <c r="BN34" s="23" t="inlineStr">
         <is>
-          <t>1.34 kg</t>
+          <t>4.61 kg</t>
         </is>
       </c>
       <c r="BO34" s="23" t="inlineStr">
         <is>
-          <t>1.34 kg</t>
+          <t>4.61 kg</t>
         </is>
       </c>
       <c r="BP34" s="23" t="inlineStr">
         <is>
-          <t>16.3 x 15.5 x 11.2 cm</t>
+          <t>44.4 x 33.4 x 19.4 cm</t>
         </is>
       </c>
       <c r="BQ34" s="23" t="inlineStr">
         <is>
-          <t>16.30 x 15.50 x 11.20 cm</t>
+          <t>44.40 x 33.40 x 19.40 cm</t>
         </is>
       </c>
       <c r="BR34" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -14023,40 +13947,40 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0FXGBT4LF</t>
+          <t>B0GDDKS6ZJ</t>
         </is>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>Domixo</t>
+          <t>HYCHIKA BETTER TOOLS FOR BETTER LIFE</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Domixo</t>
+          <t>https://www.amazon.co.uk/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/B7CD0F54-C752-439A-AD08-CA062A6946FF?lp_asin=B0GDDKS6ZJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Domixo Carpet Cleaner Machines, Hot Water Multi-Purpose Portable Spot Cleaner, Wet/dry Upholstery Cleaner, 450W &amp; Touchscreen</t>
+          <t>HYCHIKA Carpet Spot Cleaner 1800W, 17 kPa Portable Upholstery Carpet machine with Separate Tanks &amp; Self-Clean, Handheld carpe</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FXGBT4LF?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GDDKS6ZJ?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71NkpfFNvkL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51E2itCGtbL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0FXGBT4LF</t>
+          <t>B0GDDKS6ZJ</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
@@ -14070,13 +13994,13 @@
         </is>
       </c>
       <c r="O35" s="15">
-        <v>24972</v>
+        <v>37127</v>
       </c>
       <c r="P35" s="15">
-        <v>-359</v>
+        <v>-17297</v>
       </c>
       <c r="Q35" s="16">
-        <v>-0.01</v>
+        <v>-0.87</v>
       </c>
       <c r="R35" s="17" t="inlineStr">
         <is>
@@ -14085,17 +14009,17 @@
       </c>
       <c r="S35" s="18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>43</t>
         </is>
       </c>
       <c r="T35" s="15">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="U35" s="16">
-        <v>0.66</v>
+        <v>12.36</v>
       </c>
       <c r="V35" s="15">
-        <v>14978</v>
+        <v>13198</v>
       </c>
       <c r="W35" s="15" t="inlineStr">
         <is>
@@ -14103,43 +14027,43 @@
         </is>
       </c>
       <c r="X35" s="15">
-        <v>6745</v>
+        <v>7669</v>
       </c>
       <c r="Y35" s="19">
         <v>1</v>
       </c>
       <c r="Z35" s="20">
-        <v>69.99</v>
+        <v>80.22</v>
       </c>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35" s="15"/>
       <c r="AD35" s="19">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="AE35" s="15">
         <v>3</v>
       </c>
       <c r="AF35" s="21">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AG35" s="22">
-        <v>0.013999999999999999</v>
+        <v>0.0182</v>
       </c>
       <c r="AH35" s="20">
-        <v>3.43</v>
+        <v>5.33</v>
       </c>
       <c r="AI35" s="16">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="AJ35"/>
       <c r="AK35" s="13" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AL35" s="19">
-        <v>306</v>
+        <v>92</v>
       </c>
       <c r="AM35" s="13" t="inlineStr">
         <is>
@@ -14153,11 +14077,11 @@
         <v>10</v>
       </c>
       <c r="AR35" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS35" s="14" t="inlineStr">
         <is>
-          <t>qingziyu58</t>
+          <t>XLN (UK)</t>
         </is>
       </c>
       <c r="AT35" s="13" t="inlineStr">
@@ -14172,20 +14096,16 @@
       </c>
       <c r="AV35" s="14" t="inlineStr">
         <is>
-          <t>广州市 广东 510080 CN</t>
+          <t>Longgang Guangdong 518111 CN</t>
         </is>
       </c>
       <c r="AW35" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WYJ2QAIMP7S0</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGEBNOEX5B7LS</t>
         </is>
       </c>
       <c r="AX35" s="13"/>
-      <c r="AY35" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY35" s="13"/>
       <c r="AZ35" s="13"/>
       <c r="BA35" s="13"/>
       <c r="BB35" s="13"/>
@@ -14203,54 +14123,46 @@
       <c r="BF35" s="13"/>
       <c r="BG35" s="13"/>
       <c r="BH35" s="14"/>
-      <c r="BI35" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI35" s="23"/>
       <c r="BJ35" s="23" t="inlineStr">
         <is>
-          <t>4.61 kg</t>
+          <t>5.5 Kilograms</t>
         </is>
       </c>
       <c r="BK35" s="23" t="inlineStr">
         <is>
-          <t>4.61 kg</t>
+          <t>5.50 kg</t>
         </is>
       </c>
       <c r="BL35" s="23" t="inlineStr">
         <is>
-          <t>19.4 x 33.4 x 44.4 cm</t>
-        </is>
-      </c>
-      <c r="BM35" s="23" t="inlineStr">
-        <is>
-          <t>19.40 x 33.40 x 44.40 cm</t>
-        </is>
-      </c>
+          <t>19D x 43W x 33H centimetres</t>
+        </is>
+      </c>
+      <c r="BM35" s="23"/>
       <c r="BN35" s="23" t="inlineStr">
         <is>
-          <t>4.61 kg</t>
+          <t>5.53 kg</t>
         </is>
       </c>
       <c r="BO35" s="23" t="inlineStr">
         <is>
-          <t>4.61 kg</t>
+          <t>5.53 kg</t>
         </is>
       </c>
       <c r="BP35" s="23" t="inlineStr">
         <is>
-          <t>44.4 x 33.4 x 19.4 cm</t>
+          <t>43.8 x 34.6 x 20.2 cm</t>
         </is>
       </c>
       <c r="BQ35" s="23" t="inlineStr">
         <is>
-          <t>44.40 x 33.40 x 19.40 cm</t>
+          <t>43.80 x 34.60 x 20.20 cm</t>
         </is>
       </c>
       <c r="BR35" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -14261,40 +14173,40 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0GDDKS6ZJ</t>
+          <t>B0GCZXR7BP</t>
         </is>
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>HYCHIKA BETTER TOOLS FOR BETTER LIFE</t>
+          <t>uwant</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/B7CD0F54-C752-439A-AD08-CA062A6946FF?lp_asin=B0GDDKS6ZJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/uwant/b/ref=bl_dp_s_web_91770098031?ie=UTF8&amp;node=91770098031&amp;field-lbr_brands_browse-bin=uwant</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>HYCHIKA Carpet Spot Cleaner 1800W, 17 kPa Portable Upholstery Carpet machine with Separate Tanks &amp; Self-Clean, Handheld carpe</t>
+          <t>Uwant Y100 Steam Carpet Cleaner Machine, 1750W 18kPa, 7-in-1 Multi-ToolssSelf-Cleaning Hose, for Multi-Surface Spills/Pet M</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GDDKS6ZJ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GCZXR7BP?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51E2itCGtbL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0GDDKS6ZJ</t>
+          <t>B0GCZXR7BP</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
@@ -14308,13 +14220,13 @@
         </is>
       </c>
       <c r="O36" s="15">
-        <v>37127</v>
+        <v>26928</v>
       </c>
       <c r="P36" s="15">
-        <v>-17297</v>
+        <v>8550</v>
       </c>
       <c r="Q36" s="16">
-        <v>-0.87</v>
+        <v>0.24</v>
       </c>
       <c r="R36" s="17" t="inlineStr">
         <is>
@@ -14323,61 +14235,55 @@
       </c>
       <c r="S36" s="18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T36" s="15">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="U36" s="16">
-        <v>12.36</v>
+        <v>1.7</v>
       </c>
       <c r="V36" s="15">
-        <v>13198</v>
-      </c>
-      <c r="W36" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X36" s="15">
-        <v>7669</v>
-      </c>
+        <v>12375</v>
+      </c>
+      <c r="W36" s="15"/>
+      <c r="X36" s="15"/>
       <c r="Y36" s="19">
         <v>1</v>
       </c>
       <c r="Z36" s="20">
-        <v>80.22</v>
+        <v>99</v>
       </c>
       <c r="AA36"/>
       <c r="AB36"/>
       <c r="AC36" s="15"/>
       <c r="AD36" s="19">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="AE36" s="15">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="AF36" s="21">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AG36" s="22">
-        <v>0.0182</v>
+        <v>0.568</v>
       </c>
       <c r="AH36" s="20">
-        <v>5.33</v>
+        <v>5.94</v>
       </c>
       <c r="AI36" s="16">
-        <v>0.93</v>
+        <v>0.94</v>
       </c>
       <c r="AJ36"/>
       <c r="AK36" s="13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="AL36" s="19">
-        <v>92</v>
+        <v>235</v>
       </c>
       <c r="AM36" s="13" t="inlineStr">
         <is>
@@ -14391,11 +14297,11 @@
         <v>10</v>
       </c>
       <c r="AR36" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS36" s="14" t="inlineStr">
         <is>
-          <t>XLN (UK)</t>
+          <t>SpotZapper</t>
         </is>
       </c>
       <c r="AT36" s="13" t="inlineStr">
@@ -14410,16 +14316,20 @@
       </c>
       <c r="AV36" s="14" t="inlineStr">
         <is>
-          <t>Longgang Guangdong 518111 CN</t>
+          <t>芜湖市 安徽省 241399 CN</t>
         </is>
       </c>
       <c r="AW36" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGEBNOEX5B7LS</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17T2O4U8TIBEZ</t>
         </is>
       </c>
       <c r="AX36" s="13"/>
-      <c r="AY36" s="13"/>
+      <c r="AY36" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ36" s="13"/>
       <c r="BA36" s="13"/>
       <c r="BB36" s="13"/>
@@ -14437,41 +14347,49 @@
       <c r="BF36" s="13"/>
       <c r="BG36" s="13"/>
       <c r="BH36" s="14"/>
-      <c r="BI36" s="23"/>
+      <c r="BI36" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ36" s="23" t="inlineStr">
         <is>
-          <t>5.5 Kilograms</t>
+          <t>6.69 kg</t>
         </is>
       </c>
       <c r="BK36" s="23" t="inlineStr">
         <is>
-          <t>5.50 kg</t>
+          <t>6.69 kg</t>
         </is>
       </c>
       <c r="BL36" s="23" t="inlineStr">
         <is>
-          <t>19D x 43W x 33H centimetres</t>
-        </is>
-      </c>
-      <c r="BM36" s="23"/>
+          <t>35.6 x 18.3 x 31 cm</t>
+        </is>
+      </c>
+      <c r="BM36" s="23" t="inlineStr">
+        <is>
+          <t>35.60 x 18.30 x 31.00 cm</t>
+        </is>
+      </c>
       <c r="BN36" s="23" t="inlineStr">
         <is>
-          <t>5.53 kg</t>
+          <t>6.69 kg</t>
         </is>
       </c>
       <c r="BO36" s="23" t="inlineStr">
         <is>
-          <t>5.53 kg</t>
+          <t>6.69 kg</t>
         </is>
       </c>
       <c r="BP36" s="23" t="inlineStr">
         <is>
-          <t>43.8 x 34.6 x 20.2 cm</t>
+          <t>49 x 38.2 x 28.2 cm</t>
         </is>
       </c>
       <c r="BQ36" s="23" t="inlineStr">
         <is>
-          <t>43.80 x 34.60 x 20.20 cm</t>
+          <t>49.00 x 38.20 x 28.20 cm</t>
         </is>
       </c>
       <c r="BR36" s="13" t="inlineStr">
@@ -14487,40 +14405,40 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0GCZXR7BP</t>
+          <t>B08SWLD9TH</t>
         </is>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>uwant</t>
+          <t>VYTRONIX</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/uwant/b/ref=bl_dp_s_web_91770098031?ie=UTF8&amp;node=91770098031&amp;field-lbr_brands_browse-bin=uwant</t>
+          <t>https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B08SWLD9TH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Uwant Y100 Steam Carpet Cleaner Machine, 1750W 18kPa, 7-in-1 Multi-ToolssSelf-Cleaning Hose, for Multi-Surface Spills/Pet M</t>
+          <t>VYTRONIX P800CW Upright Carpet CleanersLightweight Deep Cleaning Carpet Washer, Rug &amp; Carpet Shampooer | Stains, Odours, Al</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GCZXR7BP?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B08SWLD9TH?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31UUlVUd78L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0GCZXR7BP</t>
+          <t>B08SWLD9TH</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
@@ -14534,13 +14452,13 @@
         </is>
       </c>
       <c r="O37" s="15">
-        <v>26928</v>
+        <v>48421</v>
       </c>
       <c r="P37" s="15">
-        <v>8550</v>
+        <v>14684</v>
       </c>
       <c r="Q37" s="16">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="R37" s="17" t="inlineStr">
         <is>
@@ -14549,55 +14467,63 @@
       </c>
       <c r="S37" s="18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>51</t>
         </is>
       </c>
       <c r="T37" s="15">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="U37" s="16">
-        <v>1.7</v>
+        <v>0.37</v>
       </c>
       <c r="V37" s="15">
-        <v>12375</v>
-      </c>
-      <c r="W37" s="15"/>
-      <c r="X37" s="15"/>
+        <v>11279</v>
+      </c>
+      <c r="W37" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X37" s="15">
+        <v>4000</v>
+      </c>
       <c r="Y37" s="19">
         <v>1</v>
       </c>
       <c r="Z37" s="20">
-        <v>99</v>
+        <v>79.99</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
-      <c r="AC37" s="15"/>
+      <c r="AC37" s="15">
+        <v>50</v>
+      </c>
       <c r="AD37" s="19">
-        <v>76</v>
+        <v>1536</v>
       </c>
       <c r="AE37" s="15">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="AF37" s="21">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AG37" s="22">
-        <v>0.568</v>
+        <v>0.0638</v>
       </c>
       <c r="AH37" s="20">
-        <v>5.94</v>
+        <v>6.82</v>
       </c>
       <c r="AI37" s="16">
-        <v>0.94</v>
+        <v>0.91</v>
       </c>
       <c r="AJ37"/>
       <c r="AK37" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2021-02-07</t>
         </is>
       </c>
       <c r="AL37" s="19">
-        <v>235</v>
+        <v>2040</v>
       </c>
       <c r="AM37" s="13" t="inlineStr">
         <is>
@@ -14615,7 +14541,7 @@
       </c>
       <c r="AS37" s="14" t="inlineStr">
         <is>
-          <t>SpotZapper</t>
+          <t>Vytronix</t>
         </is>
       </c>
       <c r="AT37" s="13" t="inlineStr">
@@ -14625,17 +14551,17 @@
       </c>
       <c r="AU37" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AV37" s="14" t="inlineStr">
         <is>
-          <t>芜湖市 安徽省 241399 CN</t>
+          <t>Dunstable Bedfordshire LU5 5UL GB</t>
         </is>
       </c>
       <c r="AW37" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17T2O4U8TIBEZ</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2</t>
         </is>
       </c>
       <c r="AX37" s="13"/>
@@ -14652,11 +14578,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD37" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD37" s="13"/>
       <c r="BE37" s="13"/>
       <c r="BF37" s="13"/>
       <c r="BG37" s="13"/>
@@ -14668,47 +14590,43 @@
       </c>
       <c r="BJ37" s="23" t="inlineStr">
         <is>
-          <t>6.69 kg</t>
+          <t>5.6 Kilograms</t>
         </is>
       </c>
       <c r="BK37" s="23" t="inlineStr">
         <is>
-          <t>6.69 kg</t>
+          <t>5.60 kg</t>
         </is>
       </c>
       <c r="BL37" s="23" t="inlineStr">
         <is>
-          <t>35.6 x 18.3 x 31 cm</t>
-        </is>
-      </c>
-      <c r="BM37" s="23" t="inlineStr">
-        <is>
-          <t>35.60 x 18.30 x 31.00 cm</t>
-        </is>
-      </c>
+          <t>44D x 27W x 115H centimetres</t>
+        </is>
+      </c>
+      <c r="BM37" s="23"/>
       <c r="BN37" s="23" t="inlineStr">
         <is>
-          <t>6.69 kg</t>
+          <t>6.94 kg</t>
         </is>
       </c>
       <c r="BO37" s="23" t="inlineStr">
         <is>
-          <t>6.69 kg</t>
+          <t>6.94 kg</t>
         </is>
       </c>
       <c r="BP37" s="23" t="inlineStr">
         <is>
-          <t>49 x 38.2 x 28.2 cm</t>
+          <t>103.6 x 28.3 x 25.6 cm</t>
         </is>
       </c>
       <c r="BQ37" s="23" t="inlineStr">
         <is>
-          <t>49.00 x 38.20 x 28.20 cm</t>
+          <t>103.60 x 28.30 x 25.60 cm</t>
         </is>
       </c>
       <c r="BR37" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>大号标准大件</t>
         </is>
       </c>
     </row>
@@ -14719,40 +14637,40 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B08SWLD9TH</t>
+          <t>B0DJMCBY4B</t>
         </is>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>VYTRONIX</t>
+          <t>Vacmaster</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B08SWLD9TH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/Vacmaster/page/75F2E189-B394-439E-9CC9-6F4AB03DFAE5?lp_asin=B0DJMCBY4B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>VYTRONIX P800CW Upright Carpet CleanersLightweight Deep Cleaning Carpet Washer, Rug &amp; Carpet Shampooer | Stains, Odours, Al</t>
+          <t>Vacmaster EasyClean Up Compact Carpet Spot Cleaner, CordedsSmall carpet cleaner for carpet, stairs &amp; upholstery. 550W motor</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B08SWLD9TH?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DJMCBY4B?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31UUlVUd78L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71JUj23aseL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B08SWLD9TH</t>
+          <t>B0DJMCBY4B</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
@@ -14766,13 +14684,13 @@
         </is>
       </c>
       <c r="O38" s="15">
-        <v>48421</v>
+        <v>27640</v>
       </c>
       <c r="P38" s="15">
-        <v>14684</v>
+        <v>-4064</v>
       </c>
       <c r="Q38" s="16">
-        <v>0.23</v>
+        <v>-0.17</v>
       </c>
       <c r="R38" s="17" t="inlineStr">
         <is>
@@ -14781,17 +14699,17 @@
       </c>
       <c r="S38" s="18" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>41</t>
         </is>
       </c>
       <c r="T38" s="15">
-        <v>141</v>
+        <v>186</v>
       </c>
       <c r="U38" s="16">
-        <v>0.37</v>
+        <v>0.79</v>
       </c>
       <c r="V38" s="15">
-        <v>11279</v>
+        <v>11158</v>
       </c>
       <c r="W38" s="15" t="inlineStr">
         <is>
@@ -14799,33 +14717,31 @@
         </is>
       </c>
       <c r="X38" s="15">
-        <v>4000</v>
+        <v>3319</v>
       </c>
       <c r="Y38" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z38" s="20">
-        <v>79.99</v>
+        <v>59.99</v>
       </c>
       <c r="AA38"/>
       <c r="AB38"/>
-      <c r="AC38" s="15">
-        <v>50</v>
-      </c>
+      <c r="AC38" s="15"/>
       <c r="AD38" s="19">
-        <v>1536</v>
+        <v>493</v>
       </c>
       <c r="AE38" s="15">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AF38" s="21">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AG38" s="22">
-        <v>0.0638</v>
+        <v>0.0161</v>
       </c>
       <c r="AH38" s="20">
-        <v>6.82</v>
+        <v>5.33</v>
       </c>
       <c r="AI38" s="16">
         <v>0.91</v>
@@ -14833,15 +14749,15 @@
       <c r="AJ38"/>
       <c r="AK38" s="13" t="inlineStr">
         <is>
-          <t>2021-02-07</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="AL38" s="19">
-        <v>2040</v>
+        <v>699</v>
       </c>
       <c r="AM38" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN38" s="13"/>
@@ -14855,12 +14771,12 @@
       </c>
       <c r="AS38" s="14" t="inlineStr">
         <is>
-          <t>Vytronix</t>
+          <t>Cleva Europe Ltd</t>
         </is>
       </c>
       <c r="AT38" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU38" s="13" t="inlineStr">
@@ -14870,12 +14786,12 @@
       </c>
       <c r="AV38" s="14" t="inlineStr">
         <is>
-          <t>Dunstable Bedfordshire LU5 5UL GB</t>
+          <t>Tyne and Wear NE12 8EZ GB</t>
         </is>
       </c>
       <c r="AW38" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2CDMBK5RNKHM0</t>
         </is>
       </c>
       <c r="AX38" s="13"/>
@@ -14892,7 +14808,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD38" s="13"/>
+      <c r="BD38" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE38" s="13"/>
       <c r="BF38" s="13"/>
       <c r="BG38" s="13"/>
@@ -14904,43 +14824,47 @@
       </c>
       <c r="BJ38" s="23" t="inlineStr">
         <is>
-          <t>5.6 Kilograms</t>
+          <t>3.5 kg</t>
         </is>
       </c>
       <c r="BK38" s="23" t="inlineStr">
         <is>
-          <t>5.60 kg</t>
+          <t>3.50 kg</t>
         </is>
       </c>
       <c r="BL38" s="23" t="inlineStr">
         <is>
-          <t>44D x 27W x 115H centimetres</t>
-        </is>
-      </c>
-      <c r="BM38" s="23"/>
+          <t>23 x 34 x 36 cm</t>
+        </is>
+      </c>
+      <c r="BM38" s="23" t="inlineStr">
+        <is>
+          <t>23.00 x 34.00 x 36.00 cm</t>
+        </is>
+      </c>
       <c r="BN38" s="23" t="inlineStr">
         <is>
-          <t>6.94 kg</t>
+          <t>4.77 kg</t>
         </is>
       </c>
       <c r="BO38" s="23" t="inlineStr">
         <is>
-          <t>6.94 kg</t>
+          <t>4.77 kg</t>
         </is>
       </c>
       <c r="BP38" s="23" t="inlineStr">
         <is>
-          <t>103.6 x 28.3 x 25.6 cm</t>
+          <t>37.3 x 34.4 x 23.3 cm</t>
         </is>
       </c>
       <c r="BQ38" s="23" t="inlineStr">
         <is>
-          <t>103.60 x 28.30 x 25.60 cm</t>
+          <t>37.30 x 34.40 x 23.30 cm</t>
         </is>
       </c>
       <c r="BR38" s="13" t="inlineStr">
         <is>
-          <t>大号标准大件</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -14951,40 +14875,40 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0DJMCBY4B</t>
+          <t>B0FZBSDZ26</t>
         </is>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster</t>
+          <t>VonHaus</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Vacmaster/page/75F2E189-B394-439E-9CC9-6F4AB03DFAE5?lp_asin=B0DJMCBY4B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0FZBSDZ26&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster EasyClean Up Compact Carpet Spot Cleaner, CordedsSmall carpet cleaner for carpet, stairs &amp; upholstery. 550W motor</t>
+          <t>Vonhaus Spot Cleaner 600W Handheld Carpet Cleaner with Crevice &amp; Pet Brushs1.5L Carpet Washer &amp; Sofa Cleaner Machine with S</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DJMCBY4B?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FZBSDZ26?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71JUj23aseL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41M66B54s9L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0DJMCBY4B</t>
+          <t>B0FZBSDZ26</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
@@ -14998,13 +14922,13 @@
         </is>
       </c>
       <c r="O39" s="15">
-        <v>27640</v>
+        <v>36701</v>
       </c>
       <c r="P39" s="15">
-        <v>-4064</v>
+        <v>-12727</v>
       </c>
       <c r="Q39" s="16">
-        <v>-0.17</v>
+        <v>-0.53</v>
       </c>
       <c r="R39" s="17" t="inlineStr">
         <is>
@@ -15013,65 +14937,65 @@
       </c>
       <c r="S39" s="18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T39" s="15">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="U39" s="16">
-        <v>0.79</v>
+        <v>2.28</v>
       </c>
       <c r="V39" s="15">
-        <v>11158</v>
+        <v>10778</v>
       </c>
       <c r="W39" s="15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X39" s="15">
-        <v>3319</v>
+        <v>6421</v>
       </c>
       <c r="Y39" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z39" s="20">
-        <v>59.99</v>
+        <v>69.99</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39" s="15"/>
       <c r="AD39" s="19">
-        <v>493</v>
+        <v>60</v>
       </c>
       <c r="AE39" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF39" s="21">
         <v>4.4</v>
       </c>
       <c r="AG39" s="22">
-        <v>0.0161</v>
+        <v>0.026000000000000002</v>
       </c>
       <c r="AH39" s="20">
-        <v>5.33</v>
+        <v>5.18</v>
       </c>
       <c r="AI39" s="16">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="13" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AL39" s="19">
-        <v>699</v>
+        <v>309</v>
       </c>
       <c r="AM39" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN39" s="13"/>
@@ -15085,12 +15009,12 @@
       </c>
       <c r="AS39" s="14" t="inlineStr">
         <is>
-          <t>Cleva Europe Ltd</t>
+          <t>VonHaus UK</t>
         </is>
       </c>
       <c r="AT39" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU39" s="13" t="inlineStr">
@@ -15100,12 +15024,12 @@
       </c>
       <c r="AV39" s="14" t="inlineStr">
         <is>
-          <t>Tyne and Wear NE12 8EZ GB</t>
+          <t>SALFORD Manchester M3 7BF GB</t>
         </is>
       </c>
       <c r="AW39" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2CDMBK5RNKHM0</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6</t>
         </is>
       </c>
       <c r="AX39" s="13"/>
@@ -15138,42 +15062,38 @@
       </c>
       <c r="BJ39" s="23" t="inlineStr">
         <is>
-          <t>3.5 kg</t>
+          <t>4 kg</t>
         </is>
       </c>
       <c r="BK39" s="23" t="inlineStr">
         <is>
-          <t>3.50 kg</t>
+          <t>4.00 kg</t>
         </is>
       </c>
       <c r="BL39" s="23" t="inlineStr">
         <is>
-          <t>23 x 34 x 36 cm</t>
-        </is>
-      </c>
-      <c r="BM39" s="23" t="inlineStr">
-        <is>
-          <t>23.00 x 34.00 x 36.00 cm</t>
-        </is>
-      </c>
+          <t>17.3D x 30.6W x 32.6H centimetres</t>
+        </is>
+      </c>
+      <c r="BM39" s="23"/>
       <c r="BN39" s="23" t="inlineStr">
         <is>
-          <t>4.77 kg</t>
+          <t>4.8 kg</t>
         </is>
       </c>
       <c r="BO39" s="23" t="inlineStr">
         <is>
-          <t>4.77 kg</t>
+          <t>4.80 kg</t>
         </is>
       </c>
       <c r="BP39" s="23" t="inlineStr">
         <is>
-          <t>37.3 x 34.4 x 23.3 cm</t>
+          <t>40 x 35 x 20 cm</t>
         </is>
       </c>
       <c r="BQ39" s="23" t="inlineStr">
         <is>
-          <t>37.30 x 34.40 x 23.30 cm</t>
+          <t>40.00 x 35.00 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR39" s="13" t="inlineStr">
@@ -15189,40 +15109,40 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0FZBSDZ26</t>
+          <t>B0F2J9921T</t>
         </is>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>VonHaus</t>
+          <t>Beldray</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0FZBSDZ26&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Beldray/page/8BB71969-8E70-4472-AD09-CEB0284CA329?lp_asin=B0F2J9921T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Vonhaus Spot Cleaner 600W Handheld Carpet Cleaner with Crevice &amp; Pet Brushs1.5L Carpet Washer &amp; Sofa Cleaner Machine with S</t>
+          <t>Beldray Compact Spotbuster Spot Cleaner With Spray, Scrub, Vacuum, 1.3LsExtendable Hose, Scrubbing Brush Head, Dual Tank 80</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FZBSDZ26?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0F2J9921T?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41M66B54s9L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71l-bqPqPSL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0FZBSDZ26</t>
+          <t>B0F2J9921T</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
@@ -15236,13 +15156,13 @@
         </is>
       </c>
       <c r="O40" s="15">
-        <v>36701</v>
+        <v>19977</v>
       </c>
       <c r="P40" s="15">
-        <v>-12727</v>
+        <v>582</v>
       </c>
       <c r="Q40" s="16">
-        <v>-0.53</v>
+        <v>0.03</v>
       </c>
       <c r="R40" s="17" t="inlineStr">
         <is>
@@ -15251,17 +15171,17 @@
       </c>
       <c r="S40" s="18" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>26</t>
         </is>
       </c>
       <c r="T40" s="15">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="U40" s="16">
-        <v>2.28</v>
+        <v>1.26</v>
       </c>
       <c r="V40" s="15">
-        <v>10778</v>
+        <v>10698</v>
       </c>
       <c r="W40" s="15" t="inlineStr">
         <is>
@@ -15269,43 +15189,43 @@
         </is>
       </c>
       <c r="X40" s="15">
-        <v>6421</v>
+        <v>4999</v>
       </c>
       <c r="Y40" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z40" s="20">
-        <v>69.99</v>
+        <v>49.99</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40" s="15"/>
       <c r="AD40" s="19">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="AE40" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF40" s="21">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AG40" s="22">
-        <v>0.026000000000000002</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="AH40" s="20">
         <v>5.18</v>
       </c>
       <c r="AI40" s="16">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AJ40"/>
       <c r="AK40" s="13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AL40" s="19">
-        <v>309</v>
+        <v>513</v>
       </c>
       <c r="AM40" s="13" t="inlineStr">
         <is>
@@ -15323,7 +15243,7 @@
       </c>
       <c r="AS40" s="14" t="inlineStr">
         <is>
-          <t>VonHaus UK</t>
+          <t>homeofbrands</t>
         </is>
       </c>
       <c r="AT40" s="13" t="inlineStr">
@@ -15338,12 +15258,12 @@
       </c>
       <c r="AV40" s="14" t="inlineStr">
         <is>
-          <t>SALFORD Manchester M3 7BF GB</t>
+          <t>Chadderton Oldham OL9 0DD GB</t>
         </is>
       </c>
       <c r="AW40" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2X5QKTIJPT88W</t>
         </is>
       </c>
       <c r="AX40" s="13"/>
@@ -15376,38 +15296,42 @@
       </c>
       <c r="BJ40" s="23" t="inlineStr">
         <is>
-          <t>4 kg</t>
+          <t>2.5 kg</t>
         </is>
       </c>
       <c r="BK40" s="23" t="inlineStr">
         <is>
-          <t>4.00 kg</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL40" s="23" t="inlineStr">
         <is>
-          <t>17.3D x 30.6W x 32.6H centimetres</t>
-        </is>
-      </c>
-      <c r="BM40" s="23"/>
+          <t>26 x 22 x 27 cm</t>
+        </is>
+      </c>
+      <c r="BM40" s="23" t="inlineStr">
+        <is>
+          <t>26.00 x 22.00 x 27.00 cm</t>
+        </is>
+      </c>
       <c r="BN40" s="23" t="inlineStr">
         <is>
-          <t>4.8 kg</t>
+          <t>3.56 kg</t>
         </is>
       </c>
       <c r="BO40" s="23" t="inlineStr">
         <is>
-          <t>4.80 kg</t>
+          <t>3.56 kg</t>
         </is>
       </c>
       <c r="BP40" s="23" t="inlineStr">
         <is>
-          <t>40 x 35 x 20 cm</t>
+          <t>36.3 x 35 x 21.6 cm</t>
         </is>
       </c>
       <c r="BQ40" s="23" t="inlineStr">
         <is>
-          <t>40.00 x 35.00 x 20.00 cm</t>
+          <t>36.30 x 35.00 x 21.60 cm</t>
         </is>
       </c>
       <c r="BR40" s="13" t="inlineStr">
@@ -15423,40 +15347,40 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0F2J9921T</t>
+          <t>B0CZRYCLNT</t>
         </is>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>Beldray</t>
+          <t>Daewoo</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Beldray/page/8BB71969-8E70-4472-AD09-CEB0284CA329?lp_asin=B0F2J9921T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/Daewoo/page/F8BDC7B4-3E6A-4593-ABD8-5A8336047C2A?lp_asin=B0CZRYCLNT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Beldray Compact Spotbuster Spot Cleaner With Spray, Scrub, Vacuum, 1.3LsExtendable Hose, Scrubbing Brush Head, Dual Tank 80</t>
+          <t>Daewoo Stairmaster Corded Spotwasher</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F2J9921T?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71l-bqPqPSL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0F2J9921T</t>
+          <t>B0CZRYCLNT</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
@@ -15470,13 +15394,13 @@
         </is>
       </c>
       <c r="O41" s="15">
-        <v>19977</v>
+        <v>24228</v>
       </c>
       <c r="P41" s="15">
-        <v>582</v>
+        <v>-3763</v>
       </c>
       <c r="Q41" s="16">
-        <v>0.03</v>
+        <v>-0.18</v>
       </c>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -15485,17 +15409,17 @@
       </c>
       <c r="S41" s="18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>37</t>
         </is>
       </c>
       <c r="T41" s="15">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="U41" s="16">
-        <v>1.26</v>
+        <v>0.42</v>
       </c>
       <c r="V41" s="15">
-        <v>10698</v>
+        <v>9688</v>
       </c>
       <c r="W41" s="15" t="inlineStr">
         <is>
@@ -15503,43 +15427,43 @@
         </is>
       </c>
       <c r="X41" s="15">
-        <v>4999</v>
+        <v>4503</v>
       </c>
       <c r="Y41" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z41" s="20">
-        <v>49.99</v>
+        <v>41.64</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41" s="15"/>
       <c r="AD41" s="19">
-        <v>13</v>
+        <v>315</v>
       </c>
       <c r="AE41" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF41" s="21">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AG41" s="22">
-        <v>0.009300000000000001</v>
+        <v>0.019799999999999998</v>
       </c>
       <c r="AH41" s="20">
-        <v>5.18</v>
+        <v>3.61</v>
       </c>
       <c r="AI41" s="16">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="AJ41"/>
       <c r="AK41" s="13" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="AL41" s="19">
-        <v>513</v>
+        <v>887</v>
       </c>
       <c r="AM41" s="13" t="inlineStr">
         <is>
@@ -15550,14 +15474,14 @@
       <c r="AO41" s="13"/>
       <c r="AP41"/>
       <c r="AQ41" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR41" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS41" s="14" t="inlineStr">
         <is>
-          <t>homeofbrands</t>
+          <t>UK Direct 247</t>
         </is>
       </c>
       <c r="AT41" s="13" t="inlineStr">
@@ -15572,12 +15496,12 @@
       </c>
       <c r="AV41" s="14" t="inlineStr">
         <is>
-          <t>Chadderton Oldham OL9 0DD GB</t>
+          <t>Middx TW14 9LQ GB</t>
         </is>
       </c>
       <c r="AW41" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2X5QKTIJPT88W</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24NGU5R55LIUJ</t>
         </is>
       </c>
       <c r="AX41" s="13"/>
@@ -15589,11 +15513,7 @@
       <c r="AZ41" s="13"/>
       <c r="BA41" s="13"/>
       <c r="BB41" s="13"/>
-      <c r="BC41" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC41" s="13"/>
       <c r="BD41" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15620,37 +15540,37 @@
       </c>
       <c r="BL41" s="23" t="inlineStr">
         <is>
-          <t>26 x 22 x 27 cm</t>
+          <t>35 x 20 x 23 cm</t>
         </is>
       </c>
       <c r="BM41" s="23" t="inlineStr">
         <is>
-          <t>26.00 x 22.00 x 27.00 cm</t>
+          <t>35.00 x 20.00 x 23.00 cm</t>
         </is>
       </c>
       <c r="BN41" s="23" t="inlineStr">
         <is>
-          <t>3.56 kg</t>
+          <t>3.24 kg</t>
         </is>
       </c>
       <c r="BO41" s="23" t="inlineStr">
         <is>
-          <t>3.56 kg</t>
+          <t>3.24 kg</t>
         </is>
       </c>
       <c r="BP41" s="23" t="inlineStr">
         <is>
-          <t>36.3 x 35 x 21.6 cm</t>
+          <t>41.5 x 25.5 x 20.1 cm</t>
         </is>
       </c>
       <c r="BQ41" s="23" t="inlineStr">
         <is>
-          <t>36.30 x 35.00 x 21.60 cm</t>
+          <t>41.50 x 25.50 x 20.10 cm</t>
         </is>
       </c>
       <c r="BR41" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -15661,40 +15581,40 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0CZRYCLNT</t>
+          <t>B0F6CX96F9</t>
         </is>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Daewoo</t>
+          <t>BISSELL</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Daewoo/page/F8BDC7B4-3E6A-4593-ABD8-5A8336047C2A?lp_asin=B0CZRYCLNT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0F6CX96F9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Daewoo Stairmaster Corded Spotwasher</t>
+          <t>BISSELL SpotClean Mini Corded Portable Carpet Cleaner 4149EsCompact and lightweight spot washer for quick cleanups, on-the-</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0F6CX96F9?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61SfSFyuxFL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0CZRYCLNT</t>
+          <t>B0F6CX96F9</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -15708,13 +15628,13 @@
         </is>
       </c>
       <c r="O42" s="15">
-        <v>24228</v>
+        <v>26431</v>
       </c>
       <c r="P42" s="15">
-        <v>-3763</v>
+        <v>117570</v>
       </c>
       <c r="Q42" s="16">
-        <v>-0.18</v>
+        <v>0.82</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -15723,101 +15643,89 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>202</v>
+        <v>108</v>
       </c>
       <c r="U42" s="16">
-        <v>0.42</v>
+        <v>-0.52</v>
       </c>
       <c r="V42" s="15">
-        <v>9688</v>
+        <v>9179</v>
       </c>
       <c r="W42" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X42" s="15">
-        <v>4503</v>
+        <v>4854</v>
       </c>
       <c r="Y42" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z42" s="20">
-        <v>41.64</v>
+        <v>84.99</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="15"/>
       <c r="AD42" s="19">
-        <v>315</v>
+        <v>69</v>
       </c>
       <c r="AE42" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF42" s="21">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AG42" s="22">
-        <v>0.019799999999999998</v>
+        <v>0.0556</v>
       </c>
       <c r="AH42" s="20">
         <v>3.61</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>887</v>
+        <v>460</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN42" s="13"/>
       <c r="AO42" s="13"/>
       <c r="AP42"/>
       <c r="AQ42" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR42" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
-          <t>UK Direct 247</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT42" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU42" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV42" s="14" t="inlineStr">
-        <is>
-          <t>Middx TW14 9LQ GB</t>
-        </is>
-      </c>
-      <c r="AW42" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24NGU5R55LIUJ</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU42" s="13"/>
+      <c r="AV42" s="14"/>
+      <c r="AW42" s="13"/>
       <c r="AX42" s="13"/>
       <c r="AY42" s="13" t="inlineStr">
         <is>
@@ -15827,7 +15735,11 @@
       <c r="AZ42" s="13"/>
       <c r="BA42" s="13"/>
       <c r="BB42" s="13"/>
-      <c r="BC42" s="13"/>
+      <c r="BC42" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD42" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15844,42 +15756,42 @@
       </c>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>2.5 kg</t>
+          <t>3.1 kg</t>
         </is>
       </c>
       <c r="BK42" s="23" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
+          <t>3.10 kg</t>
         </is>
       </c>
       <c r="BL42" s="23" t="inlineStr">
         <is>
-          <t>35 x 20 x 23 cm</t>
+          <t>25 x 34 x 30.8 cm</t>
         </is>
       </c>
       <c r="BM42" s="23" t="inlineStr">
         <is>
-          <t>35.00 x 20.00 x 23.00 cm</t>
+          <t>25.00 x 34.00 x 30.80 cm</t>
         </is>
       </c>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>4.49 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>4.49 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>41.5 x 25.5 x 20.1 cm</t>
+          <t>33.3 x 33.1 x 22.2 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>41.50 x 25.50 x 20.10 cm</t>
+          <t>33.30 x 33.10 x 22.20 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
@@ -15895,45 +15807,45 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B00T31O22Y</t>
         </is>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>BISSELL</t>
+          <t>Rug Doctor</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0753NXDPR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/RugDoctor/page/8161ECDA-1080-4AC4-92F6-141201B689F6?lp_asin=B00T31O22Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Oxygen Boost Formula Booster for SpotClean 1L 1134NsA cleaning solution booster for use on carpet, upholstery, area</t>
+          <t>Rug Doctor Portable Spot Cleaner (1100W)sThe Telegraph’s 2025 “Best Buy” - 2X Suction - Motorised Brush - Handheld Tools fo</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0753NXDPR?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B00T31O22Y?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51-YKuNNnoL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81pdye0z+dL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B00T31O22Y</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
         <is>
-          <t>Pet Supplies:Dogs:Litter &amp; Housetraining:Odour &amp; Stain Removers:Stain Removers</t>
+          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Carpet Washers</t>
         </is>
       </c>
       <c r="N43" s="14" t="inlineStr">
@@ -15942,13 +15854,13 @@
         </is>
       </c>
       <c r="O43" s="15">
-        <v>1429</v>
+        <v>24517</v>
       </c>
       <c r="P43" s="15">
-        <v>-6963</v>
+        <v>47293</v>
       </c>
       <c r="Q43" s="16">
-        <v>-0.35</v>
+        <v>0.66</v>
       </c>
       <c r="R43" s="17" t="inlineStr">
         <is>
@@ -15961,59 +15873,53 @@
         </is>
       </c>
       <c r="T43" s="15">
-        <v>935</v>
+        <v>68</v>
       </c>
       <c r="U43" s="16">
-        <v>-0.28</v>
+        <v>-0.63</v>
       </c>
       <c r="V43" s="15">
-        <v>9322</v>
-      </c>
-      <c r="W43" s="15" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="X43" s="15">
-        <v>1994</v>
-      </c>
+        <v>8092</v>
+      </c>
+      <c r="W43" s="15"/>
+      <c r="X43" s="15"/>
       <c r="Y43" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z43" s="20">
-        <v>9.97</v>
+        <v>99.17</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="15">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="AD43" s="19">
-        <v>9356</v>
+        <v>3749</v>
       </c>
       <c r="AE43" s="15">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="AF43" s="21">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AG43" s="22">
-        <v>0.1155</v>
+        <v>0</v>
       </c>
       <c r="AH43" s="20">
-        <v>3.1</v>
+        <v>6.39</v>
       </c>
       <c r="AI43" s="16">
-        <v>0.69</v>
+        <v>0.95</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2019-12-19</t>
+          <t>2015-02-10</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>2455</v>
+        <v>4229</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
@@ -16027,7 +15933,7 @@
         <v>10</v>
       </c>
       <c r="AR43" s="19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
@@ -16043,11 +15949,7 @@
       <c r="AV43" s="14"/>
       <c r="AW43" s="13"/>
       <c r="AX43" s="13"/>
-      <c r="AY43" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY43" s="13"/>
       <c r="AZ43" s="13"/>
       <c r="BA43" s="13"/>
       <c r="BB43" s="13"/>
@@ -16065,54 +15967,50 @@
       <c r="BF43" s="13"/>
       <c r="BG43" s="13"/>
       <c r="BH43" s="14"/>
-      <c r="BI43" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI43" s="23"/>
       <c r="BJ43" s="23" t="inlineStr">
         <is>
-          <t>1.1 kg</t>
+          <t>7.45 kg</t>
         </is>
       </c>
       <c r="BK43" s="23" t="inlineStr">
         <is>
-          <t>1.10 kg</t>
+          <t>7.45 kg</t>
         </is>
       </c>
       <c r="BL43" s="23" t="inlineStr">
         <is>
-          <t>7 x 12 x 23.8 cm</t>
+          <t>41 x 28 x 40 cm</t>
         </is>
       </c>
       <c r="BM43" s="23" t="inlineStr">
         <is>
-          <t>7.00 x 12.00 x 23.80 cm</t>
+          <t>41.00 x 28.00 x 40.00 cm</t>
         </is>
       </c>
       <c r="BN43" s="23" t="inlineStr">
         <is>
-          <t>1.1 kg</t>
+          <t>9.05 kg</t>
         </is>
       </c>
       <c r="BO43" s="23" t="inlineStr">
         <is>
-          <t>1.10 kg</t>
+          <t>9.05 kg</t>
         </is>
       </c>
       <c r="BP43" s="23" t="inlineStr">
         <is>
-          <t>23.5 x 11.9 x 6.9 cm</t>
+          <t>45.2 x 44.6 x 32.2 cm</t>
         </is>
       </c>
       <c r="BQ43" s="23" t="inlineStr">
         <is>
-          <t>23.50 x 11.90 x 6.90 cm</t>
+          <t>45.20 x 44.60 x 32.20 cm</t>
         </is>
       </c>
       <c r="BR43" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -16123,40 +16021,40 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0F6CX96F9</t>
+          <t>B0GGB47WMZ</t>
         </is>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>BISSELL</t>
+          <t>Olvy</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0F6CX96F9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Olvy/page/42DFC99A-3581-46D9-A283-1EF2C68CD7B1?lp_asin=B0GGB47WMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>BISSELL SpotClean Mini Corded Portable Carpet Cleaner 4149EsCompact and lightweight spot washer for quick cleanups, on-the-</t>
+          <t>Olvy Carpet Cleaner Upholstery Spot Washer Deep Stain Removals6 Piece Kit | Basic 17000Pa | Sofa &amp; Vehicle Interior | Easy</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F6CX96F9?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GGB47WMZ?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61SfSFyuxFL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71hexWEmuXL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0F6CX96F9</t>
+          <t>B0GGB47WMZ</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
@@ -16170,13 +16068,13 @@
         </is>
       </c>
       <c r="O44" s="15">
-        <v>26431</v>
+        <v>17017</v>
       </c>
       <c r="P44" s="15">
-        <v>117570</v>
+        <v>42538</v>
       </c>
       <c r="Q44" s="16">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
@@ -16185,17 +16083,17 @@
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>27</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="U44" s="16">
-        <v>-0.52</v>
+        <v>0.66</v>
       </c>
       <c r="V44" s="15">
-        <v>9179</v>
+        <v>7436</v>
       </c>
       <c r="W44" s="15" t="inlineStr">
         <is>
@@ -16203,71 +16101,83 @@
         </is>
       </c>
       <c r="X44" s="15">
-        <v>4854</v>
+        <v>2590</v>
       </c>
       <c r="Y44" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z44" s="20">
-        <v>84.99</v>
+        <v>42.49</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44" s="15"/>
       <c r="AD44" s="19">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="AE44" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AF44" s="21">
         <v>4.5</v>
       </c>
       <c r="AG44" s="22">
-        <v>0.0556</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="AH44" s="20">
-        <v>3.61</v>
+        <v>5.63</v>
       </c>
       <c r="AI44" s="16">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>460</v>
+        <v>232</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN44" s="13"/>
       <c r="AO44" s="13"/>
       <c r="AP44"/>
       <c r="AQ44" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR44" s="19">
         <v>1</v>
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Olvy</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU44" s="13"/>
-      <c r="AV44" s="14"/>
-      <c r="AW44" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU44" s="13" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="AV44" s="14" t="inlineStr">
+        <is>
+          <t>NIJMEGEN Gelderland 6511DX NL</t>
+        </is>
+      </c>
+      <c r="AW44" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G</t>
+        </is>
+      </c>
       <c r="AX44" s="13"/>
       <c r="AY44" s="13" t="inlineStr">
         <is>
@@ -16277,11 +16187,7 @@
       <c r="AZ44" s="13"/>
       <c r="BA44" s="13"/>
       <c r="BB44" s="13"/>
-      <c r="BC44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC44" s="13"/>
       <c r="BD44" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16298,47 +16204,47 @@
       </c>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>3.1 kg</t>
+          <t>3.5 kg</t>
         </is>
       </c>
       <c r="BK44" s="23" t="inlineStr">
         <is>
-          <t>3.10 kg</t>
+          <t>3.50 kg</t>
         </is>
       </c>
       <c r="BL44" s="23" t="inlineStr">
         <is>
-          <t>25 x 34 x 30.8 cm</t>
+          <t>30.7 x 28 x 17.1 cm</t>
         </is>
       </c>
       <c r="BM44" s="23" t="inlineStr">
         <is>
-          <t>25.00 x 34.00 x 30.80 cm</t>
+          <t>30.70 x 28.00 x 17.10 cm</t>
         </is>
       </c>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>4.49 kg</t>
+          <t>5.52 kg</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>4.49 kg</t>
+          <t>5.52 kg</t>
         </is>
       </c>
       <c r="BP44" s="23" t="inlineStr">
         <is>
-          <t>33.3 x 33.1 x 22.2 cm</t>
+          <t>43.6 x 34.8 x 26.6 cm</t>
         </is>
       </c>
       <c r="BQ44" s="23" t="inlineStr">
         <is>
-          <t>33.30 x 33.10 x 22.20 cm</t>
+          <t>43.60 x 34.80 x 26.60 cm</t>
         </is>
       </c>
       <c r="BR44" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -16349,40 +16255,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B00T31O22Y</t>
+          <t>B09QLD7MVM</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>Rug Doctor</t>
+          <t>Ewbank</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/RugDoctor/page/8161ECDA-1080-4AC4-92F6-141201B689F6?lp_asin=B00T31O22Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Ewbank/page/379635B0-DB01-48B5-9749-216DB75EB5AC?lp_asin=B09QLD7MVM&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Rug Doctor Portable Spot Cleaner (1100W)sThe Telegraph’s 2025 “Best Buy” - 2X Suction - Motorised Brush - Handheld Tools fo</t>
+          <t>Ewbank EW3070 HYDROC1 Wet &amp; Dry Carpet Cleaner, Lightweight with Trigger Release, Ideal for Cleaning Carpets &amp; Rugs, Removes</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B00T31O22Y?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B09QLD7MVM?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81pdye0z+dL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31an1tA1N+L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B00T31O22Y</t>
+          <t>B09QLD7MVM</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -16392,80 +16298,86 @@
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="O45" s="15">
-        <v>24517</v>
+        <v>20605</v>
       </c>
       <c r="P45" s="15">
-        <v>47293</v>
+        <v>18842</v>
       </c>
       <c r="Q45" s="16">
-        <v>0.66</v>
+        <v>0.48</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
-          <t>Carpet Washers</t>
+          <t>Carpet Washers
+Carpet Cleaners</t>
         </is>
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>42
+80</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="U45" s="16">
-        <v>-0.63</v>
+        <v>1.79</v>
       </c>
       <c r="V45" s="15">
-        <v>8092</v>
-      </c>
-      <c r="W45" s="15"/>
-      <c r="X45" s="15"/>
+        <v>5779</v>
+      </c>
+      <c r="W45" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X45" s="15">
+        <v>3400</v>
+      </c>
       <c r="Y45" s="19">
         <v>1</v>
       </c>
       <c r="Z45" s="20">
-        <v>99.17</v>
+        <v>67.99</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
-      <c r="AC45" s="15">
-        <v>82</v>
-      </c>
+      <c r="AC45" s="15"/>
       <c r="AD45" s="19">
-        <v>3749</v>
+        <v>67</v>
       </c>
       <c r="AE45" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF45" s="21">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AG45" s="22">
-        <v>0</v>
+        <v>0.0118</v>
       </c>
       <c r="AH45" s="20">
-        <v>6.39</v>
+        <v>6.85</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2015-02-10</t>
+          <t>2022-02-02</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>4229</v>
+        <v>1680</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN45" s="13"/>
@@ -16475,23 +16387,39 @@
         <v>10</v>
       </c>
       <c r="AR45" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Go Shop Direct</t>
         </is>
       </c>
       <c r="AT45" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU45" s="13"/>
-      <c r="AV45" s="14"/>
-      <c r="AW45" s="13"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU45" s="13" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AV45" s="14" t="inlineStr">
+        <is>
+          <t>Bristol BS8 2NT GB</t>
+        </is>
+      </c>
+      <c r="AW45" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A29F1JIJWJQSEI</t>
+        </is>
+      </c>
       <c r="AX45" s="13"/>
-      <c r="AY45" s="13"/>
+      <c r="AY45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ45" s="13"/>
       <c r="BA45" s="13"/>
       <c r="BB45" s="13"/>
@@ -16509,45 +16437,49 @@
       <c r="BF45" s="13"/>
       <c r="BG45" s="13"/>
       <c r="BH45" s="14"/>
-      <c r="BI45" s="23"/>
+      <c r="BI45" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>7.45 kg</t>
+          <t>5.7 Kilograms</t>
         </is>
       </c>
       <c r="BK45" s="23" t="inlineStr">
         <is>
-          <t>7.45 kg</t>
+          <t>5.70 kg</t>
         </is>
       </c>
       <c r="BL45" s="23" t="inlineStr">
         <is>
-          <t>41 x 28 x 40 cm</t>
+          <t>25 x 42 x 108 cm</t>
         </is>
       </c>
       <c r="BM45" s="23" t="inlineStr">
         <is>
-          <t>41.00 x 28.00 x 40.00 cm</t>
+          <t>25.00 x 42.00 x 108.00 cm</t>
         </is>
       </c>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>9.05 kg</t>
+          <t>8.2 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>9.05 kg</t>
+          <t>8.20 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>45.2 x 44.6 x 32.2 cm</t>
+          <t>93 x 31.5 x 28.5 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>45.20 x 44.60 x 32.20 cm</t>
+          <t>93.00 x 31.50 x 28.50 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
@@ -16563,40 +16495,40 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0GGB47WMZ</t>
+          <t>B0B4JST7J8</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Olvy</t>
+          <t>Swan</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Olvy/page/42DFC99A-3581-46D9-A283-1EF2C68CD7B1?lp_asin=B0GGB47WMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/SwanProductsLtd/page/69D73DEE-49FE-4AEE-B38D-1948D70187CB?lp_asin=B0B4JST7J8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Olvy Carpet Cleaner Upholstery Spot Washer Deep Stain Removals6 Piece Kit | Basic 17000Pa | Sofa &amp; Vehicle Interior | Easy</t>
+          <t>Swan TV’s Queen of Clean Handheld Carpet Cleaner with 5m Power Cord, 480ml Water Tank, 500W, Pink, SC18410QOCN</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GGB47WMZ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71hexWEmuXL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0GGB47WMZ</t>
+          <t>B0B4JST7J8</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -16610,13 +16542,13 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>17017</v>
+        <v>23222</v>
       </c>
       <c r="P46" s="15">
-        <v>42538</v>
+        <v>3597</v>
       </c>
       <c r="Q46" s="16">
-        <v>0.71</v>
+        <v>0.13</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
@@ -16625,17 +16557,17 @@
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="U46" s="16">
-        <v>0.66</v>
+        <v>0.04</v>
       </c>
       <c r="V46" s="15">
-        <v>7436</v>
+        <v>5320</v>
       </c>
       <c r="W46" s="15" t="inlineStr">
         <is>
@@ -16643,93 +16575,81 @@
         </is>
       </c>
       <c r="X46" s="15">
-        <v>2590</v>
+        <v>2183</v>
       </c>
       <c r="Y46" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z46" s="20">
-        <v>42.49</v>
+        <v>33.33</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46" s="15"/>
       <c r="AD46" s="19">
-        <v>29</v>
+        <v>509</v>
       </c>
       <c r="AE46" s="15">
         <v>1</v>
       </c>
       <c r="AF46" s="21">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AG46" s="22">
-        <v>0.005699999999999999</v>
+        <v>0.0075</v>
       </c>
       <c r="AH46" s="20">
-        <v>5.63</v>
+        <v>3.43</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>232</v>
+        <v>1538</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN46" s="13"/>
       <c r="AO46" s="13"/>
       <c r="AP46"/>
       <c r="AQ46" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR46" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Olvy</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU46" s="13" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="AV46" s="14" t="inlineStr">
-        <is>
-          <t>NIJMEGEN Gelderland 6511DX NL</t>
-        </is>
-      </c>
-      <c r="AW46" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU46" s="13"/>
+      <c r="AV46" s="14"/>
+      <c r="AW46" s="13"/>
       <c r="AX46" s="13"/>
-      <c r="AY46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
-      <c r="BC46" s="13"/>
+      <c r="BC46" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD46" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16739,54 +16659,50 @@
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
       <c r="BH46" s="14"/>
-      <c r="BI46" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI46" s="23"/>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>3.5 kg</t>
+          <t>2.58 kg</t>
         </is>
       </c>
       <c r="BK46" s="23" t="inlineStr">
         <is>
-          <t>3.50 kg</t>
+          <t>2.58 kg</t>
         </is>
       </c>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>30.7 x 28 x 17.1 cm</t>
+          <t>23 x 20 x 34 cm</t>
         </is>
       </c>
       <c r="BM46" s="23" t="inlineStr">
         <is>
-          <t>30.70 x 28.00 x 17.10 cm</t>
+          <t>23.00 x 20.00 x 34.00 cm</t>
         </is>
       </c>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>5.52 kg</t>
+          <t>3.29 kg</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>5.52 kg</t>
+          <t>3.29 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>43.6 x 34.8 x 26.6 cm</t>
+          <t>41.1 x 24.6 x 20.6 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>43.60 x 34.80 x 26.60 cm</t>
+          <t>41.10 x 24.60 x 20.60 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -16797,40 +16713,40 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B09QLD7MVM</t>
+          <t>B0H98GCFZB</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>Ewbank</t>
+          <t>STARRYBOT</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Ewbank/page/379635B0-DB01-48B5-9749-216DB75EB5AC?lp_asin=B09QLD7MVM&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=STARRYBOT</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Ewbank EW3070 HYDROC1 Wet &amp; Dry Carpet Cleaner, Lightweight with Trigger Release, Ideal for Cleaning Carpets &amp; Rugs, Removes</t>
+          <t>STARRYBOT Steam Carpet and Upholstery Cleaner, 1500W, 18KPasSteam cleaner tackles stains on rugs, stairs, sofas and car sea</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B09QLD7MVM?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H98GCFZB?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31an1tA1N+L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61faJrtabwL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B09QLD7MVM</t>
+          <t>B0H98GCFZB</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
@@ -16840,86 +16756,76 @@
       </c>
       <c r="N47" s="14" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="O47" s="15">
-        <v>20605</v>
+        <v>21128</v>
       </c>
       <c r="P47" s="15">
-        <v>18842</v>
+        <v>454144</v>
       </c>
       <c r="Q47" s="16">
-        <v>0.48</v>
+        <v>0.96</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
-          <t>Carpet Washers
-Carpet Cleaners</t>
+          <t>Carpet Washers</t>
         </is>
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>42
-80</t>
+          <t>33</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>85</v>
-      </c>
-      <c r="U47" s="16">
-        <v>1.79</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="U47" s="16"/>
       <c r="V47" s="15">
-        <v>5779</v>
-      </c>
-      <c r="W47" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X47" s="15">
-        <v>3400</v>
-      </c>
+        <v>2695</v>
+      </c>
+      <c r="W47" s="15"/>
+      <c r="X47" s="15"/>
       <c r="Y47" s="19">
         <v>1</v>
       </c>
       <c r="Z47" s="20">
-        <v>67.99</v>
+        <v>109.9</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47" s="15"/>
       <c r="AD47" s="19">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="AE47" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF47" s="21">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AG47" s="22">
-        <v>0.0118</v>
+        <v>0.0857</v>
       </c>
       <c r="AH47" s="20">
-        <v>6.85</v>
+        <v>5.33</v>
       </c>
       <c r="AI47" s="16">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="13" t="inlineStr">
         <is>
-          <t>2022-02-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AL47" s="19">
-        <v>1680</v>
+        <v>13</v>
       </c>
       <c r="AM47" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN47" s="13"/>
@@ -16929,39 +16835,35 @@
         <v>10</v>
       </c>
       <c r="AR47" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>Go Shop Direct</t>
+          <t>HEYWORK</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU47" s="13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV47" s="14" t="inlineStr">
         <is>
-          <t>Bristol BS8 2NT GB</t>
+          <t>宁波市 浙江 315000 CN</t>
         </is>
       </c>
       <c r="AW47" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A29F1JIJWJQSEI</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A190HADBP97HLJ</t>
         </is>
       </c>
       <c r="AX47" s="13"/>
-      <c r="AY47" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY47" s="13"/>
       <c r="AZ47" s="13"/>
       <c r="BA47" s="13"/>
       <c r="BB47" s="13"/>
@@ -16979,49 +16881,45 @@
       <c r="BF47" s="13"/>
       <c r="BG47" s="13"/>
       <c r="BH47" s="14"/>
-      <c r="BI47" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI47" s="23"/>
       <c r="BJ47" s="23" t="inlineStr">
         <is>
-          <t>5.7 Kilograms</t>
+          <t>2.5 kg</t>
         </is>
       </c>
       <c r="BK47" s="23" t="inlineStr">
         <is>
-          <t>5.70 kg</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL47" s="23" t="inlineStr">
         <is>
-          <t>25 x 42 x 108 cm</t>
+          <t>30 x 20 x 25 cm</t>
         </is>
       </c>
       <c r="BM47" s="23" t="inlineStr">
         <is>
-          <t>25.00 x 42.00 x 108.00 cm</t>
+          <t>30.00 x 20.00 x 25.00 cm</t>
         </is>
       </c>
       <c r="BN47" s="23" t="inlineStr">
         <is>
-          <t>8.2 kg</t>
+          <t>5.17 kg</t>
         </is>
       </c>
       <c r="BO47" s="23" t="inlineStr">
         <is>
-          <t>8.20 kg</t>
+          <t>5.17 kg</t>
         </is>
       </c>
       <c r="BP47" s="23" t="inlineStr">
         <is>
-          <t>93 x 31.5 x 28.5 cm</t>
+          <t>43.3 x 35 x 20 cm</t>
         </is>
       </c>
       <c r="BQ47" s="23" t="inlineStr">
         <is>
-          <t>93.00 x 31.50 x 28.50 cm</t>
+          <t>43.30 x 35.00 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR47" s="13" t="inlineStr">
@@ -17037,40 +16935,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0B4JST7J8</t>
+          <t>B01LX6WOFS</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Swan</t>
+          <t>Ecozone</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/SwanProductsLtd/page/69D73DEE-49FE-4AEE-B38D-1948D70187CB?lp_asin=B0B4JST7J8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Ecozone/page/B457F3C7-F7E8-45B1-B9BB-D317BE4CAE57?lp_asin=B01LX6WOFS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Swan TV’s Queen of Clean Handheld Carpet Cleaner with 5m Power Cord, 480ml Water Tank, 500W, Pink, SC18410QOCN</t>
+          <t>EcoZone Carpet Shampoo Solution, Deep Cleans Upholstery, Manual &amp; Machine Cleaning, Fresh Cotton Scent, 3-in-1 Plant Based St</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B01LX6WOFS?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61toYqbNVBL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0B4JST7J8</t>
+          <t>B01LX6WOFS</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -17084,13 +16982,13 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>23222</v>
+        <v>20031</v>
       </c>
       <c r="P48" s="15">
-        <v>3597</v>
+        <v>10502</v>
       </c>
       <c r="Q48" s="16">
-        <v>0.13</v>
+        <v>0.35</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -17099,61 +16997,63 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>133</v>
+        <v>218</v>
       </c>
       <c r="U48" s="16">
-        <v>0.04</v>
+        <v>0.41</v>
       </c>
       <c r="V48" s="15">
-        <v>5320</v>
+        <v>1552</v>
       </c>
       <c r="W48" s="15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X48" s="15">
-        <v>2183</v>
+        <v>762</v>
       </c>
       <c r="Y48" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>33.33</v>
+        <v>7.12</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
-      <c r="AC48" s="15"/>
+      <c r="AC48" s="15">
+        <v>9</v>
+      </c>
       <c r="AD48" s="19">
-        <v>509</v>
+        <v>903</v>
       </c>
       <c r="AE48" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF48" s="21">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AG48" s="22">
-        <v>0.0075</v>
+        <v>0.0092</v>
       </c>
       <c r="AH48" s="20">
-        <v>3.43</v>
+        <v>3.1</v>
       </c>
       <c r="AI48" s="16">
-        <v>0.91</v>
+        <v>0.56</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2017-05-30</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>1538</v>
+        <v>3388</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
@@ -17167,7 +17067,7 @@
         <v>10</v>
       </c>
       <c r="AR48" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
@@ -17183,7 +17083,11 @@
       <c r="AV48" s="14"/>
       <c r="AW48" s="13"/>
       <c r="AX48" s="13"/>
-      <c r="AY48" s="13"/>
+      <c r="AY48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ48" s="13"/>
       <c r="BA48" s="13"/>
       <c r="BB48" s="13"/>
@@ -17201,50 +17105,54 @@
       <c r="BF48" s="13"/>
       <c r="BG48" s="13"/>
       <c r="BH48" s="14"/>
-      <c r="BI48" s="23"/>
+      <c r="BI48" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ48" s="23" t="inlineStr">
         <is>
-          <t>2.58 kg</t>
+          <t>0.43 g</t>
         </is>
       </c>
       <c r="BK48" s="23" t="inlineStr">
         <is>
-          <t>2.58 kg</t>
+          <t>0.43 g</t>
         </is>
       </c>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>23 x 20 x 34 cm</t>
+          <t>8 x 12 x 25 cm</t>
         </is>
       </c>
       <c r="BM48" s="23" t="inlineStr">
         <is>
-          <t>23.00 x 20.00 x 34.00 cm</t>
+          <t>8.00 x 12.00 x 25.00 cm</t>
         </is>
       </c>
       <c r="BN48" s="23" t="inlineStr">
         <is>
-          <t>3.29 kg</t>
+          <t>1.06 kg</t>
         </is>
       </c>
       <c r="BO48" s="23" t="inlineStr">
         <is>
-          <t>3.29 kg</t>
+          <t>1.06 kg</t>
         </is>
       </c>
       <c r="BP48" s="23" t="inlineStr">
         <is>
-          <t>41.1 x 24.6 x 20.6 cm</t>
+          <t>23.4 x 11.9 x 7 cm</t>
         </is>
       </c>
       <c r="BQ48" s="23" t="inlineStr">
         <is>
-          <t>41.10 x 24.60 x 20.60 cm</t>
+          <t>23.40 x 11.90 x 7.00 cm</t>
         </is>
       </c>
       <c r="BR48" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -17255,554 +17163,104 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0H98GCFZB</t>
+          <t>B0CFV97B7G</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>STARRYBOT</t>
-        </is>
-      </c>
+      <c r="F49" s="14"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=STARRYBOT</t>
+          <t>https://www.amazon.co.ukundefined</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>STARRYBOT Steam Carpet and Upholstery Cleaner, 1500W, 18KPasSteam cleaner tackles stains on rugs, stairs, sofas and car sea</t>
+          <t>Shark StainStriker Pet Stain and Spot Cleaner, White/Turquoise PX200UKTsCompact Carpet and Upholstery Cleaner with Powerful</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H98GCFZB?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CFV97B7G?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61faJrtabwL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71lEpDoSWgL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0H98GCFZB</t>
-        </is>
-      </c>
-      <c r="M49" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Carpet Washers</t>
-        </is>
-      </c>
-      <c r="N49" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O49" s="15">
-        <v>21128</v>
-      </c>
-      <c r="P49" s="15">
-        <v>454144</v>
-      </c>
-      <c r="Q49" s="16">
-        <v>0.96</v>
-      </c>
-      <c r="R49" s="17" t="inlineStr">
-        <is>
-          <t>Carpet Washers</t>
-        </is>
-      </c>
-      <c r="S49" s="18" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="T49" s="15">
-        <v>35</v>
-      </c>
+          <t>B0CFV97B7G</t>
+        </is>
+      </c>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="15"/>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="16"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="15"/>
       <c r="U49" s="16"/>
-      <c r="V49" s="15">
-        <v>2695</v>
-      </c>
+      <c r="V49" s="15"/>
       <c r="W49" s="15"/>
       <c r="X49" s="15"/>
-      <c r="Y49" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z49" s="20">
-        <v>109.9</v>
-      </c>
+      <c r="Y49" s="19"/>
+      <c r="Z49" s="20"/>
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49" s="15"/>
       <c r="AD49" s="19">
-        <v>42</v>
-      </c>
-      <c r="AE49" s="15">
-        <v>3</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="AE49" s="15"/>
       <c r="AF49" s="21">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AG49" s="22">
-        <v>0.0857</v>
-      </c>
-      <c r="AH49" s="20">
-        <v>5.33</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH49" s="20"/>
       <c r="AI49" s="16">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="AJ49"/>
-      <c r="AK49" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AL49" s="19">
-        <v>13</v>
-      </c>
-      <c r="AM49" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK49" s="13"/>
+      <c r="AL49" s="19"/>
+      <c r="AM49" s="13"/>
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
       <c r="AP49"/>
-      <c r="AQ49" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR49" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS49" s="14" t="inlineStr">
-        <is>
-          <t>HEYWORK</t>
-        </is>
-      </c>
-      <c r="AT49" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU49" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV49" s="14" t="inlineStr">
-        <is>
-          <t>宁波市 浙江 315000 CN</t>
-        </is>
-      </c>
-      <c r="AW49" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A190HADBP97HLJ</t>
-        </is>
-      </c>
+      <c r="AQ49" s="19"/>
+      <c r="AR49" s="19"/>
+      <c r="AS49" s="14"/>
+      <c r="AT49" s="13"/>
+      <c r="AU49" s="13"/>
+      <c r="AV49" s="14"/>
+      <c r="AW49" s="13"/>
       <c r="AX49" s="13"/>
       <c r="AY49" s="13"/>
       <c r="AZ49" s="13"/>
       <c r="BA49" s="13"/>
       <c r="BB49" s="13"/>
-      <c r="BC49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC49" s="13"/>
+      <c r="BD49" s="13"/>
       <c r="BE49" s="13"/>
       <c r="BF49" s="13"/>
       <c r="BG49" s="13"/>
       <c r="BH49" s="14"/>
       <c r="BI49" s="23"/>
-      <c r="BJ49" s="23" t="inlineStr">
-        <is>
-          <t>2.5 kg</t>
-        </is>
-      </c>
-      <c r="BK49" s="23" t="inlineStr">
-        <is>
-          <t>2.50 kg</t>
-        </is>
-      </c>
-      <c r="BL49" s="23" t="inlineStr">
-        <is>
-          <t>30 x 20 x 25 cm</t>
-        </is>
-      </c>
-      <c r="BM49" s="23" t="inlineStr">
-        <is>
-          <t>30.00 x 20.00 x 25.00 cm</t>
-        </is>
-      </c>
-      <c r="BN49" s="23" t="inlineStr">
-        <is>
-          <t>5.17 kg</t>
-        </is>
-      </c>
-      <c r="BO49" s="23" t="inlineStr">
-        <is>
-          <t>5.17 kg</t>
-        </is>
-      </c>
-      <c r="BP49" s="23" t="inlineStr">
-        <is>
-          <t>43.3 x 35 x 20 cm</t>
-        </is>
-      </c>
-      <c r="BQ49" s="23" t="inlineStr">
-        <is>
-          <t>43.30 x 35.00 x 20.00 cm</t>
-        </is>
-      </c>
-      <c r="BR49" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B01LX6WOFS</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>Ecozone</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/stores/Ecozone/page/B457F3C7-F7E8-45B1-B9BB-D317BE4CAE57?lp_asin=B01LX6WOFS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>EcoZone Carpet Shampoo Solution, Deep Cleans Upholstery, Manual &amp; Machine Cleaning, Fresh Cotton Scent, 3-in-1 Plant Based St</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B01LX6WOFS?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61toYqbNVBL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B01LX6WOFS</t>
-        </is>
-      </c>
-      <c r="M50" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Carpet Washers</t>
-        </is>
-      </c>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O50" s="15">
-        <v>20031</v>
-      </c>
-      <c r="P50" s="15">
-        <v>10502</v>
-      </c>
-      <c r="Q50" s="16">
-        <v>0.35</v>
-      </c>
-      <c r="R50" s="17" t="inlineStr">
-        <is>
-          <t>Carpet Washers</t>
-        </is>
-      </c>
-      <c r="S50" s="18" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="T50" s="15">
-        <v>218</v>
-      </c>
-      <c r="U50" s="16">
-        <v>0.41</v>
-      </c>
-      <c r="V50" s="15">
-        <v>1552</v>
-      </c>
-      <c r="W50" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X50" s="15">
-        <v>762</v>
-      </c>
-      <c r="Y50" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="20">
-        <v>7.12</v>
-      </c>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50" s="15">
-        <v>9</v>
-      </c>
-      <c r="AD50" s="19">
-        <v>903</v>
-      </c>
-      <c r="AE50" s="15">
-        <v>2</v>
-      </c>
-      <c r="AF50" s="21">
-        <v>4.4</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0.0092</v>
-      </c>
-      <c r="AH50" s="20">
-        <v>3.1</v>
-      </c>
-      <c r="AI50" s="16">
-        <v>0.56</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="13" t="inlineStr">
-        <is>
-          <t>2017-05-30</t>
-        </is>
-      </c>
-      <c r="AL50" s="19">
-        <v>3388</v>
-      </c>
-      <c r="AM50" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR50" s="19">
-        <v>2</v>
-      </c>
-      <c r="AS50" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT50" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU50" s="13"/>
-      <c r="AV50" s="14"/>
-      <c r="AW50" s="13"/>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
-      <c r="BJ50" s="23" t="inlineStr">
-        <is>
-          <t>0.43 g</t>
-        </is>
-      </c>
-      <c r="BK50" s="23" t="inlineStr">
-        <is>
-          <t>0.43 g</t>
-        </is>
-      </c>
-      <c r="BL50" s="23" t="inlineStr">
-        <is>
-          <t>8 x 12 x 25 cm</t>
-        </is>
-      </c>
-      <c r="BM50" s="23" t="inlineStr">
-        <is>
-          <t>8.00 x 12.00 x 25.00 cm</t>
-        </is>
-      </c>
-      <c r="BN50" s="23" t="inlineStr">
-        <is>
-          <t>1.06 kg</t>
-        </is>
-      </c>
-      <c r="BO50" s="23" t="inlineStr">
-        <is>
-          <t>1.06 kg</t>
-        </is>
-      </c>
-      <c r="BP50" s="23" t="inlineStr">
-        <is>
-          <t>23.4 x 11.9 x 7 cm</t>
-        </is>
-      </c>
-      <c r="BQ50" s="23" t="inlineStr">
-        <is>
-          <t>23.40 x 11.90 x 7.00 cm</t>
-        </is>
-      </c>
-      <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>小包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0CFV97B7G</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Shark StainStriker Pet Stain and Spot Cleaner, White/Turquoise PX200UKTsCompact Carpet and Upholstery Cleaner with Powerful</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0CFV97B7G?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71lEpDoSWgL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0CFV97B7G</t>
-        </is>
-      </c>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19"/>
-      <c r="Z51" s="20"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="15"/>
-      <c r="AD51" s="19">
-        <v>456</v>
-      </c>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="21">
-        <v>4.4</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51" s="13"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="19"/>
-      <c r="AS51" s="14"/>
-      <c r="AT51" s="13"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51" s="23"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51" s="23"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51" s="13"/>
+      <c r="BJ49" s="23"/>
+      <c r="BK49" s="23"/>
+      <c r="BL49" s="23"/>
+      <c r="BM49" s="23"/>
+      <c r="BN49" s="23"/>
+      <c r="BO49" s="23"/>
+      <c r="BP49" s="23"/>
+      <c r="BQ49" s="23"/>
+      <c r="BR49" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18042,143 +17500,129 @@
     <hyperlink ref="L33" r:id="rId232" tooltip="https://www.amazon.co.uk/dp/B0BX3CS1MS"/>
     <hyperlink ref="M33" r:id="rId233" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N33" r:id="rId234"/>
-    <hyperlink ref="C34" r:id="rId235" tooltip="https://www.amazon.co.uk/dp/B0FNX6YLCJ"/>
-    <hyperlink ref="G34" r:id="rId236" tooltip="https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0FNX6YLCJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J34" r:id="rId237" tooltip="https://www.amazon.co.uk/dp/B0FNX6YLCJ?psc=1"/>
-    <hyperlink ref="K34" r:id="rId238" tooltip="https://images-na.ssl-images-amazon.com/images/I/71SuXoGPIQL._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId239" tooltip="https://www.amazon.co.uk/dp/B0FNX6YLCJ"/>
+    <hyperlink ref="C34" r:id="rId235" tooltip="https://www.amazon.co.uk/dp/B0FXGBT4LF"/>
+    <hyperlink ref="G34" r:id="rId236" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Domixo"/>
+    <hyperlink ref="J34" r:id="rId237" tooltip="https://www.amazon.co.uk/dp/B0FXGBT4LF?psc=1"/>
+    <hyperlink ref="K34" r:id="rId238" tooltip="https://images-na.ssl-images-amazon.com/images/I/71NkpfFNvkL._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId239" tooltip="https://www.amazon.co.uk/dp/B0FXGBT4LF"/>
     <hyperlink ref="M34" r:id="rId240" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N34" r:id="rId241"/>
-    <hyperlink ref="C35" r:id="rId242" tooltip="https://www.amazon.co.uk/dp/B0FXGBT4LF"/>
-    <hyperlink ref="G35" r:id="rId243" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Domixo"/>
-    <hyperlink ref="J35" r:id="rId244" tooltip="https://www.amazon.co.uk/dp/B0FXGBT4LF?psc=1"/>
-    <hyperlink ref="K35" r:id="rId245" tooltip="https://images-na.ssl-images-amazon.com/images/I/71NkpfFNvkL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId246" tooltip="https://www.amazon.co.uk/dp/B0FXGBT4LF"/>
-    <hyperlink ref="M35" r:id="rId247" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N35" r:id="rId248"/>
-    <hyperlink ref="AW35" r:id="rId249" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WYJ2QAIMP7S0"/>
-    <hyperlink ref="C36" r:id="rId250" tooltip="https://www.amazon.co.uk/dp/B0GDDKS6ZJ"/>
-    <hyperlink ref="G36" r:id="rId251" tooltip="https://www.amazon.co.uk/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/B7CD0F54-C752-439A-AD08-CA062A6946FF?lp_asin=B0GDDKS6ZJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J36" r:id="rId252" tooltip="https://www.amazon.co.uk/dp/B0GDDKS6ZJ?psc=1"/>
-    <hyperlink ref="K36" r:id="rId253" tooltip="https://m.media-amazon.com/images/I/51E2itCGtbL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId254" tooltip="https://www.amazon.co.uk/dp/B0GDDKS6ZJ"/>
-    <hyperlink ref="M36" r:id="rId255" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N36" r:id="rId256"/>
-    <hyperlink ref="AW36" r:id="rId257" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGEBNOEX5B7LS"/>
-    <hyperlink ref="C37" r:id="rId258" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP"/>
-    <hyperlink ref="G37" r:id="rId259" tooltip="https://www.amazon.co.uk/uwant/b/ref=bl_dp_s_web_91770098031?ie=UTF8&amp;node=91770098031&amp;field-lbr_brands_browse-bin=uwant"/>
-    <hyperlink ref="J37" r:id="rId260" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP?psc=1"/>
-    <hyperlink ref="K37" r:id="rId261" tooltip="https://images-na.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId262" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP"/>
-    <hyperlink ref="M37" r:id="rId263" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N37" r:id="rId264"/>
-    <hyperlink ref="AW37" r:id="rId265" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17T2O4U8TIBEZ"/>
-    <hyperlink ref="C38" r:id="rId266" tooltip="https://www.amazon.co.uk/dp/B08SWLD9TH"/>
-    <hyperlink ref="G38" r:id="rId267" tooltip="https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B08SWLD9TH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J38" r:id="rId268" tooltip="https://www.amazon.co.uk/dp/B08SWLD9TH?psc=1"/>
-    <hyperlink ref="K38" r:id="rId269" tooltip="https://m.media-amazon.com/images/I/31UUlVUd78L._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId270" tooltip="https://www.amazon.co.uk/dp/B08SWLD9TH"/>
-    <hyperlink ref="M38" r:id="rId271" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N38" r:id="rId272"/>
-    <hyperlink ref="AW38" r:id="rId273" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2"/>
-    <hyperlink ref="C39" r:id="rId274" tooltip="https://www.amazon.co.uk/dp/B0DJMCBY4B"/>
-    <hyperlink ref="G39" r:id="rId275" tooltip="https://www.amazon.co.uk/stores/Vacmaster/page/75F2E189-B394-439E-9CC9-6F4AB03DFAE5?lp_asin=B0DJMCBY4B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J39" r:id="rId276" tooltip="https://www.amazon.co.uk/dp/B0DJMCBY4B?psc=1"/>
-    <hyperlink ref="K39" r:id="rId277" tooltip="https://images-na.ssl-images-amazon.com/images/I/71JUj23aseL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId278" tooltip="https://www.amazon.co.uk/dp/B0DJMCBY4B"/>
-    <hyperlink ref="M39" r:id="rId279" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N39" r:id="rId280"/>
-    <hyperlink ref="AW39" r:id="rId281" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2CDMBK5RNKHM0"/>
-    <hyperlink ref="C40" r:id="rId282" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26"/>
-    <hyperlink ref="G40" r:id="rId283" tooltip="https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0FZBSDZ26&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J40" r:id="rId284" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26?psc=1"/>
-    <hyperlink ref="K40" r:id="rId285" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41M66B54s9L._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId286" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26"/>
-    <hyperlink ref="M40" r:id="rId287" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N40" r:id="rId288"/>
-    <hyperlink ref="AW40" r:id="rId289" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6"/>
-    <hyperlink ref="C41" r:id="rId290" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
-    <hyperlink ref="G41" r:id="rId291" tooltip="https://www.amazon.co.uk/stores/Beldray/page/8BB71969-8E70-4472-AD09-CEB0284CA329?lp_asin=B0F2J9921T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J41" r:id="rId292" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T?psc=1"/>
-    <hyperlink ref="K41" r:id="rId293" tooltip="https://images-na.ssl-images-amazon.com/images/I/71l-bqPqPSL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId294" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
-    <hyperlink ref="M41" r:id="rId295" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N41" r:id="rId296"/>
-    <hyperlink ref="AW41" r:id="rId297" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2X5QKTIJPT88W"/>
-    <hyperlink ref="C42" r:id="rId298" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
-    <hyperlink ref="G42" r:id="rId299" tooltip="https://www.amazon.co.uk/stores/Daewoo/page/F8BDC7B4-3E6A-4593-ABD8-5A8336047C2A?lp_asin=B0CZRYCLNT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J42" r:id="rId300" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1"/>
-    <hyperlink ref="K42" r:id="rId301" tooltip="https://images-na.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId302" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
-    <hyperlink ref="M42" r:id="rId303" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N42" r:id="rId304"/>
-    <hyperlink ref="AW42" r:id="rId305" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24NGU5R55LIUJ"/>
-    <hyperlink ref="C43" r:id="rId306" tooltip="https://www.amazon.co.uk/dp/B0753NXDPR"/>
-    <hyperlink ref="G43" r:id="rId307" tooltip="https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0753NXDPR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J43" r:id="rId308" tooltip="https://www.amazon.co.uk/dp/B0753NXDPR?psc=1"/>
-    <hyperlink ref="K43" r:id="rId309" tooltip="https://images-na.ssl-images-amazon.com/images/I/51-YKuNNnoL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId310" tooltip="https://www.amazon.co.uk/dp/B0753NXDPR"/>
-    <hyperlink ref="M43" r:id="rId311" tooltip="https://www.amazon.co.uk/b?node=27348822031"/>
+    <hyperlink ref="AW34" r:id="rId242" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WYJ2QAIMP7S0"/>
+    <hyperlink ref="C35" r:id="rId243" tooltip="https://www.amazon.co.uk/dp/B0GDDKS6ZJ"/>
+    <hyperlink ref="G35" r:id="rId244" tooltip="https://www.amazon.co.uk/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/B7CD0F54-C752-439A-AD08-CA062A6946FF?lp_asin=B0GDDKS6ZJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J35" r:id="rId245" tooltip="https://www.amazon.co.uk/dp/B0GDDKS6ZJ?psc=1"/>
+    <hyperlink ref="K35" r:id="rId246" tooltip="https://m.media-amazon.com/images/I/51E2itCGtbL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId247" tooltip="https://www.amazon.co.uk/dp/B0GDDKS6ZJ"/>
+    <hyperlink ref="M35" r:id="rId248" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N35" r:id="rId249"/>
+    <hyperlink ref="AW35" r:id="rId250" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGEBNOEX5B7LS"/>
+    <hyperlink ref="C36" r:id="rId251" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP"/>
+    <hyperlink ref="G36" r:id="rId252" tooltip="https://www.amazon.co.uk/uwant/b/ref=bl_dp_s_web_91770098031?ie=UTF8&amp;node=91770098031&amp;field-lbr_brands_browse-bin=uwant"/>
+    <hyperlink ref="J36" r:id="rId253" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP?psc=1"/>
+    <hyperlink ref="K36" r:id="rId254" tooltip="https://images-na.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId255" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP"/>
+    <hyperlink ref="M36" r:id="rId256" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N36" r:id="rId257"/>
+    <hyperlink ref="AW36" r:id="rId258" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17T2O4U8TIBEZ"/>
+    <hyperlink ref="C37" r:id="rId259" tooltip="https://www.amazon.co.uk/dp/B08SWLD9TH"/>
+    <hyperlink ref="G37" r:id="rId260" tooltip="https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B08SWLD9TH&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J37" r:id="rId261" tooltip="https://www.amazon.co.uk/dp/B08SWLD9TH?psc=1"/>
+    <hyperlink ref="K37" r:id="rId262" tooltip="https://m.media-amazon.com/images/I/31UUlVUd78L._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId263" tooltip="https://www.amazon.co.uk/dp/B08SWLD9TH"/>
+    <hyperlink ref="M37" r:id="rId264" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N37" r:id="rId265"/>
+    <hyperlink ref="AW37" r:id="rId266" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2"/>
+    <hyperlink ref="C38" r:id="rId267" tooltip="https://www.amazon.co.uk/dp/B0DJMCBY4B"/>
+    <hyperlink ref="G38" r:id="rId268" tooltip="https://www.amazon.co.uk/stores/Vacmaster/page/75F2E189-B394-439E-9CC9-6F4AB03DFAE5?lp_asin=B0DJMCBY4B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J38" r:id="rId269" tooltip="https://www.amazon.co.uk/dp/B0DJMCBY4B?psc=1"/>
+    <hyperlink ref="K38" r:id="rId270" tooltip="https://images-na.ssl-images-amazon.com/images/I/71JUj23aseL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId271" tooltip="https://www.amazon.co.uk/dp/B0DJMCBY4B"/>
+    <hyperlink ref="M38" r:id="rId272" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N38" r:id="rId273"/>
+    <hyperlink ref="AW38" r:id="rId274" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2CDMBK5RNKHM0"/>
+    <hyperlink ref="C39" r:id="rId275" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26"/>
+    <hyperlink ref="G39" r:id="rId276" tooltip="https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0FZBSDZ26&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J39" r:id="rId277" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26?psc=1"/>
+    <hyperlink ref="K39" r:id="rId278" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/41M66B54s9L._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId279" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26"/>
+    <hyperlink ref="M39" r:id="rId280" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N39" r:id="rId281"/>
+    <hyperlink ref="AW39" r:id="rId282" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6"/>
+    <hyperlink ref="C40" r:id="rId283" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
+    <hyperlink ref="G40" r:id="rId284" tooltip="https://www.amazon.co.uk/stores/Beldray/page/8BB71969-8E70-4472-AD09-CEB0284CA329?lp_asin=B0F2J9921T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J40" r:id="rId285" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T?psc=1"/>
+    <hyperlink ref="K40" r:id="rId286" tooltip="https://images-na.ssl-images-amazon.com/images/I/71l-bqPqPSL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId287" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
+    <hyperlink ref="M40" r:id="rId288" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N40" r:id="rId289"/>
+    <hyperlink ref="AW40" r:id="rId290" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2X5QKTIJPT88W"/>
+    <hyperlink ref="C41" r:id="rId291" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
+    <hyperlink ref="G41" r:id="rId292" tooltip="https://www.amazon.co.uk/stores/Daewoo/page/F8BDC7B4-3E6A-4593-ABD8-5A8336047C2A?lp_asin=B0CZRYCLNT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J41" r:id="rId293" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1"/>
+    <hyperlink ref="K41" r:id="rId294" tooltip="https://images-na.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId295" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
+    <hyperlink ref="M41" r:id="rId296" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N41" r:id="rId297"/>
+    <hyperlink ref="AW41" r:id="rId298" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24NGU5R55LIUJ"/>
+    <hyperlink ref="C42" r:id="rId299" tooltip="https://www.amazon.co.uk/dp/B0F6CX96F9"/>
+    <hyperlink ref="G42" r:id="rId300" tooltip="https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0F6CX96F9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J42" r:id="rId301" tooltip="https://www.amazon.co.uk/dp/B0F6CX96F9?psc=1"/>
+    <hyperlink ref="K42" r:id="rId302" tooltip="https://images-na.ssl-images-amazon.com/images/I/61SfSFyuxFL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId303" tooltip="https://www.amazon.co.uk/dp/B0F6CX96F9"/>
+    <hyperlink ref="M42" r:id="rId304" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N42" r:id="rId305"/>
+    <hyperlink ref="C43" r:id="rId306" tooltip="https://www.amazon.co.uk/dp/B00T31O22Y"/>
+    <hyperlink ref="G43" r:id="rId307" tooltip="https://www.amazon.co.uk/stores/RugDoctor/page/8161ECDA-1080-4AC4-92F6-141201B689F6?lp_asin=B00T31O22Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J43" r:id="rId308" tooltip="https://www.amazon.co.uk/dp/B00T31O22Y?psc=1"/>
+    <hyperlink ref="K43" r:id="rId309" tooltip="https://images-na.ssl-images-amazon.com/images/I/81pdye0z+dL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId310" tooltip="https://www.amazon.co.uk/dp/B00T31O22Y"/>
+    <hyperlink ref="M43" r:id="rId311" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N43" r:id="rId312"/>
-    <hyperlink ref="C44" r:id="rId313" tooltip="https://www.amazon.co.uk/dp/B0F6CX96F9"/>
-    <hyperlink ref="G44" r:id="rId314" tooltip="https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0F6CX96F9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J44" r:id="rId315" tooltip="https://www.amazon.co.uk/dp/B0F6CX96F9?psc=1"/>
-    <hyperlink ref="K44" r:id="rId316" tooltip="https://images-na.ssl-images-amazon.com/images/I/61SfSFyuxFL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId317" tooltip="https://www.amazon.co.uk/dp/B0F6CX96F9"/>
+    <hyperlink ref="C44" r:id="rId313" tooltip="https://www.amazon.co.uk/dp/B0GGB47WMZ"/>
+    <hyperlink ref="G44" r:id="rId314" tooltip="https://www.amazon.co.uk/stores/Olvy/page/42DFC99A-3581-46D9-A283-1EF2C68CD7B1?lp_asin=B0GGB47WMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J44" r:id="rId315" tooltip="https://www.amazon.co.uk/dp/B0GGB47WMZ?psc=1"/>
+    <hyperlink ref="K44" r:id="rId316" tooltip="https://images-na.ssl-images-amazon.com/images/I/71hexWEmuXL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId317" tooltip="https://www.amazon.co.uk/dp/B0GGB47WMZ"/>
     <hyperlink ref="M44" r:id="rId318" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N44" r:id="rId319"/>
-    <hyperlink ref="C45" r:id="rId320" tooltip="https://www.amazon.co.uk/dp/B00T31O22Y"/>
-    <hyperlink ref="G45" r:id="rId321" tooltip="https://www.amazon.co.uk/stores/RugDoctor/page/8161ECDA-1080-4AC4-92F6-141201B689F6?lp_asin=B00T31O22Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J45" r:id="rId322" tooltip="https://www.amazon.co.uk/dp/B00T31O22Y?psc=1"/>
-    <hyperlink ref="K45" r:id="rId323" tooltip="https://images-na.ssl-images-amazon.com/images/I/81pdye0z+dL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId324" tooltip="https://www.amazon.co.uk/dp/B00T31O22Y"/>
-    <hyperlink ref="M45" r:id="rId325" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N45" r:id="rId326"/>
-    <hyperlink ref="C46" r:id="rId327" tooltip="https://www.amazon.co.uk/dp/B0GGB47WMZ"/>
-    <hyperlink ref="G46" r:id="rId328" tooltip="https://www.amazon.co.uk/stores/Olvy/page/42DFC99A-3581-46D9-A283-1EF2C68CD7B1?lp_asin=B0GGB47WMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J46" r:id="rId329" tooltip="https://www.amazon.co.uk/dp/B0GGB47WMZ?psc=1"/>
-    <hyperlink ref="K46" r:id="rId330" tooltip="https://images-na.ssl-images-amazon.com/images/I/71hexWEmuXL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId331" tooltip="https://www.amazon.co.uk/dp/B0GGB47WMZ"/>
-    <hyperlink ref="M46" r:id="rId332" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N46" r:id="rId333"/>
-    <hyperlink ref="AW46" r:id="rId334" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G"/>
-    <hyperlink ref="C47" r:id="rId335" tooltip="https://www.amazon.co.uk/dp/B09QLD7MVM"/>
-    <hyperlink ref="G47" r:id="rId336" tooltip="https://www.amazon.co.uk/stores/Ewbank/page/379635B0-DB01-48B5-9749-216DB75EB5AC?lp_asin=B09QLD7MVM&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J47" r:id="rId337" tooltip="https://www.amazon.co.uk/dp/B09QLD7MVM?psc=1"/>
-    <hyperlink ref="K47" r:id="rId338" tooltip="https://m.media-amazon.com/images/I/31an1tA1N+L._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId339" tooltip="https://www.amazon.co.uk/dp/B09QLD7MVM"/>
-    <hyperlink ref="M47" r:id="rId340" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N47" r:id="rId341"/>
-    <hyperlink ref="AW47" r:id="rId342" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A29F1JIJWJQSEI"/>
-    <hyperlink ref="C48" r:id="rId343" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
-    <hyperlink ref="G48" r:id="rId344" tooltip="https://www.amazon.co.uk/stores/SwanProductsLtd/page/69D73DEE-49FE-4AEE-B38D-1948D70187CB?lp_asin=B0B4JST7J8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J48" r:id="rId345" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1"/>
-    <hyperlink ref="K48" r:id="rId346" tooltip="https://images-na.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId347" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
-    <hyperlink ref="M48" r:id="rId348" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N48" r:id="rId349"/>
-    <hyperlink ref="C49" r:id="rId350" tooltip="https://www.amazon.co.uk/dp/B0H98GCFZB"/>
-    <hyperlink ref="G49" r:id="rId351" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=STARRYBOT"/>
-    <hyperlink ref="J49" r:id="rId352" tooltip="https://www.amazon.co.uk/dp/B0H98GCFZB?psc=1"/>
-    <hyperlink ref="K49" r:id="rId353" tooltip="https://images-na.ssl-images-amazon.com/images/I/61faJrtabwL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId354" tooltip="https://www.amazon.co.uk/dp/B0H98GCFZB"/>
-    <hyperlink ref="M49" r:id="rId355" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N49" r:id="rId356"/>
-    <hyperlink ref="AW49" r:id="rId357" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A190HADBP97HLJ"/>
-    <hyperlink ref="C50" r:id="rId358" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS"/>
-    <hyperlink ref="G50" r:id="rId359" tooltip="https://www.amazon.co.uk/stores/Ecozone/page/B457F3C7-F7E8-45B1-B9BB-D317BE4CAE57?lp_asin=B01LX6WOFS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J50" r:id="rId360" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS?psc=1"/>
-    <hyperlink ref="K50" r:id="rId361" tooltip="https://images-na.ssl-images-amazon.com/images/I/61toYqbNVBL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId362" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS"/>
-    <hyperlink ref="M50" r:id="rId363" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N50" r:id="rId364"/>
-    <hyperlink ref="C51" r:id="rId365" tooltip="https://www.amazon.co.uk/dp/B0CFV97B7G"/>
-    <hyperlink ref="G51" r:id="rId366" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J51" r:id="rId367" tooltip="https://www.amazon.co.uk/dp/B0CFV97B7G?psc=1"/>
-    <hyperlink ref="K51" r:id="rId368" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71lEpDoSWgL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId369" tooltip="https://www.amazon.co.uk/dp/B0CFV97B7G"/>
+    <hyperlink ref="AW44" r:id="rId320" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G"/>
+    <hyperlink ref="C45" r:id="rId321" tooltip="https://www.amazon.co.uk/dp/B09QLD7MVM"/>
+    <hyperlink ref="G45" r:id="rId322" tooltip="https://www.amazon.co.uk/stores/Ewbank/page/379635B0-DB01-48B5-9749-216DB75EB5AC?lp_asin=B09QLD7MVM&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J45" r:id="rId323" tooltip="https://www.amazon.co.uk/dp/B09QLD7MVM?psc=1"/>
+    <hyperlink ref="K45" r:id="rId324" tooltip="https://m.media-amazon.com/images/I/31an1tA1N+L._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId325" tooltip="https://www.amazon.co.uk/dp/B09QLD7MVM"/>
+    <hyperlink ref="M45" r:id="rId326" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N45" r:id="rId327"/>
+    <hyperlink ref="AW45" r:id="rId328" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A29F1JIJWJQSEI"/>
+    <hyperlink ref="C46" r:id="rId329" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
+    <hyperlink ref="G46" r:id="rId330" tooltip="https://www.amazon.co.uk/stores/SwanProductsLtd/page/69D73DEE-49FE-4AEE-B38D-1948D70187CB?lp_asin=B0B4JST7J8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J46" r:id="rId331" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1"/>
+    <hyperlink ref="K46" r:id="rId332" tooltip="https://images-na.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId333" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
+    <hyperlink ref="M46" r:id="rId334" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N46" r:id="rId335"/>
+    <hyperlink ref="C47" r:id="rId336" tooltip="https://www.amazon.co.uk/dp/B0H98GCFZB"/>
+    <hyperlink ref="G47" r:id="rId337" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=STARRYBOT"/>
+    <hyperlink ref="J47" r:id="rId338" tooltip="https://www.amazon.co.uk/dp/B0H98GCFZB?psc=1"/>
+    <hyperlink ref="K47" r:id="rId339" tooltip="https://images-na.ssl-images-amazon.com/images/I/61faJrtabwL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId340" tooltip="https://www.amazon.co.uk/dp/B0H98GCFZB"/>
+    <hyperlink ref="M47" r:id="rId341" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N47" r:id="rId342"/>
+    <hyperlink ref="AW47" r:id="rId343" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A190HADBP97HLJ"/>
+    <hyperlink ref="C48" r:id="rId344" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS"/>
+    <hyperlink ref="G48" r:id="rId345" tooltip="https://www.amazon.co.uk/stores/Ecozone/page/B457F3C7-F7E8-45B1-B9BB-D317BE4CAE57?lp_asin=B01LX6WOFS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J48" r:id="rId346" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS?psc=1"/>
+    <hyperlink ref="K48" r:id="rId347" tooltip="https://images-na.ssl-images-amazon.com/images/I/61toYqbNVBL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId348" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS"/>
+    <hyperlink ref="M48" r:id="rId349" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N48" r:id="rId350"/>
+    <hyperlink ref="C49" r:id="rId351" tooltip="https://www.amazon.co.uk/dp/B0CFV97B7G"/>
+    <hyperlink ref="G49" r:id="rId352" tooltip="https://www.amazon.co.ukundefined"/>
+    <hyperlink ref="J49" r:id="rId353" tooltip="https://www.amazon.co.uk/dp/B0CFV97B7G?psc=1"/>
+    <hyperlink ref="K49" r:id="rId354" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71lEpDoSWgL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId355" tooltip="https://www.amazon.co.uk/dp/B0CFV97B7G"/>
   </hyperlinks>
-  <drawing r:id="rId370"/>
+  <drawing r:id="rId356"/>
 </worksheet>
 </file>
 
@@ -18248,7 +17692,7 @@
         <v>98.80206479174083</v>
       </c>
       <c r="G2" s="22">
-        <v>0.49585172109443953</v>
+        <v>0.5199650941400465</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18258,18 +17702,18 @@
         </is>
       </c>
       <c r="B3" s="15">
-        <v>5312</v>
+        <v>4408</v>
       </c>
       <c r="C3" s="15">
-        <v>750246</v>
+        <v>735185</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="20">
-        <v>141.23606927710844</v>
+        <v>166.7842558983666</v>
       </c>
       <c r="G3" s="22">
-        <v>0.1339553650233262</v>
+        <v>0.1165644171779141</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18279,18 +17723,18 @@
         </is>
       </c>
       <c r="B4" s="15">
-        <v>5319</v>
+        <v>4384</v>
       </c>
       <c r="C4" s="15">
-        <v>371459</v>
+        <v>362137</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="20">
-        <v>69.83624741492761</v>
+        <v>82.60424270072993</v>
       </c>
       <c r="G4" s="22">
-        <v>0.1341318875299458</v>
+        <v>0.11592976517876032</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18311,7 +17755,7 @@
         <v>50.036058700209644</v>
       </c>
       <c r="G5" s="22">
-        <v>0.06014373975539024</v>
+        <v>0.0630685424159086</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18332,7 +17776,7 @@
         <v>224.5968992248062</v>
       </c>
       <c r="G6" s="22">
-        <v>0.013012230487958644</v>
+        <v>0.013645017981806644</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18353,7 +17797,7 @@
         <v>61.7753164556962</v>
       </c>
       <c r="G7" s="22">
-        <v>0.039843651494136934</v>
+        <v>0.04178125661095832</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18374,7 +17818,7 @@
         <v>49.990283400809716</v>
       </c>
       <c r="G8" s="22">
-        <v>0.03114361366788551</v>
+        <v>0.03265813412312249</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18395,7 +17839,7 @@
         <v>89.99140401146131</v>
       </c>
       <c r="G9" s="22">
-        <v>0.008800907830034043</v>
+        <v>0.009228897821028136</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18416,7 +17860,7 @@
         <v>75.0</v>
       </c>
       <c r="G10" s="22">
-        <v>0.010288740385827765</v>
+        <v>0.010789083985614555</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18437,7 +17881,7 @@
         <v>57.98927613941019</v>
       </c>
       <c r="G11" s="22">
-        <v>0.009406127852729795</v>
+        <v>0.009863549820181934</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18458,7 +17902,7 @@
         <v>66.48089171974522</v>
       </c>
       <c r="G12" s="22">
-        <v>0.007918295296936073</v>
+        <v>0.008303363655595515</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18479,7 +17923,7 @@
         <v>56.989830508474576</v>
       </c>
       <c r="G13" s="22">
-        <v>0.007439162778968604</v>
+        <v>0.0078009308229320925</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18500,7 +17944,7 @@
         <v>69.99065420560747</v>
       </c>
       <c r="G14" s="22">
-        <v>0.005396545202370445</v>
+        <v>0.005658980325788026</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18521,7 +17965,7 @@
         <v>79.98787878787878</v>
       </c>
       <c r="G15" s="22">
-        <v>0.004160887656033287</v>
+        <v>0.004363232494182356</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18542,7 +17986,7 @@
         <v>99.0</v>
       </c>
       <c r="G16" s="22">
-        <v>0.0031521876182070358</v>
+        <v>0.003305479162259361</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18563,7 +18007,7 @@
         <v>59.98924731182796</v>
       </c>
       <c r="G17" s="22">
-        <v>0.004690455175892069</v>
+        <v>0.004918552993441929</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18584,7 +18028,7 @@
         <v>69.98701298701299</v>
       </c>
       <c r="G18" s="22">
-        <v>0.003883495145631068</v>
+        <v>0.004072350327903533</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18605,7 +18049,7 @@
         <v>49.99065420560748</v>
       </c>
       <c r="G19" s="22">
-        <v>0.005396545202370445</v>
+        <v>0.005658980325788026</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18626,7 +18070,7 @@
         <v>47.960396039603964</v>
       </c>
       <c r="G20" s="22">
-        <v>0.005093935191022569</v>
+        <v>0.005341654326211128</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18647,7 +18091,7 @@
         <v>42.49142857142857</v>
       </c>
       <c r="G21" s="22">
-        <v>0.00441306266548985</v>
+        <v>0.004627670827163106</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18668,7 +18112,7 @@
         <v>67.98823529411764</v>
       </c>
       <c r="G22" s="22">
-        <v>0.002143487580380784</v>
+        <v>0.0022477258303363655</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18689,7 +18133,7 @@
         <v>40.0</v>
       </c>
       <c r="G23" s="22">
-        <v>0.003353927625772286</v>
+        <v>0.0035170298286439604</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18710,7 +18154,7 @@
         <v>77.0</v>
       </c>
       <c r="G24" s="22">
-        <v>0.00088261253309797</v>
+        <v>0.0009255341654326212</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18731,7 +18175,7 @@
         <v>7.1192660550458715</v>
       </c>
       <c r="G25" s="22">
-        <v>0.005497415206153071</v>
+        <v>0.005764755658980326</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18814,18 +18258,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>30673</v>
+        <v>28834</v>
       </c>
       <c r="C2" s="15">
-        <v>3003715</v>
+        <v>2979332</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>97.92700420565318</v>
+        <v>103.32704446139974</v>
       </c>
       <c r="G2" s="22">
-        <v>0.7734964065061153</v>
+        <v>0.7624814893166914</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18846,7 +18290,7 @@
         <v>299.99038461538464</v>
       </c>
       <c r="G3" s="22">
-        <v>0.013113100491741268</v>
+        <v>0.013750793314998943</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18867,7 +18311,7 @@
         <v>50.036058700209644</v>
       </c>
       <c r="G4" s="22">
-        <v>0.06014373975539024</v>
+        <v>0.0630685424159086</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18888,7 +18332,7 @@
         <v>61.7753164556962</v>
       </c>
       <c r="G5" s="22">
-        <v>0.039843651494136934</v>
+        <v>0.04178125661095832</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18909,7 +18353,7 @@
         <v>49.990283400809716</v>
       </c>
       <c r="G6" s="22">
-        <v>0.03114361366788551</v>
+        <v>0.03265813412312249</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18930,7 +18374,7 @@
         <v>97.0</v>
       </c>
       <c r="G7" s="22">
-        <v>0.01207918295296936</v>
+        <v>0.012666596149777871</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18951,7 +18395,7 @@
         <v>174.9918699186992</v>
       </c>
       <c r="G8" s="22">
-        <v>0.006203505232631446</v>
+        <v>0.006505182991326423</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18972,7 +18416,7 @@
         <v>57.98927613941019</v>
       </c>
       <c r="G9" s="22">
-        <v>0.009406127852729795</v>
+        <v>0.009863549820181934</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18993,7 +18437,7 @@
         <v>66.48089171974522</v>
       </c>
       <c r="G10" s="22">
-        <v>0.007918295296936073</v>
+        <v>0.008303363655595515</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19014,7 +18458,7 @@
         <v>56.989830508474576</v>
       </c>
       <c r="G11" s="22">
-        <v>0.007439162778968604</v>
+        <v>0.0078009308229320925</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19035,7 +18479,7 @@
         <v>69.99065420560747</v>
       </c>
       <c r="G12" s="22">
-        <v>0.005396545202370445</v>
+        <v>0.005658980325788026</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19056,7 +18500,7 @@
         <v>79.98787878787878</v>
       </c>
       <c r="G13" s="22">
-        <v>0.004160887656033287</v>
+        <v>0.004363232494182356</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19077,7 +18521,7 @@
         <v>99.0</v>
       </c>
       <c r="G14" s="22">
-        <v>0.0031521876182070358</v>
+        <v>0.003305479162259361</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19098,7 +18542,7 @@
         <v>59.98924731182796</v>
       </c>
       <c r="G15" s="22">
-        <v>0.004690455175892069</v>
+        <v>0.004918552993441929</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19119,7 +18563,7 @@
         <v>69.98701298701299</v>
       </c>
       <c r="G16" s="22">
-        <v>0.003883495145631068</v>
+        <v>0.004072350327903533</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19140,7 +18584,7 @@
         <v>49.99065420560748</v>
       </c>
       <c r="G17" s="22">
-        <v>0.005396545202370445</v>
+        <v>0.005658980325788026</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19161,7 +18605,7 @@
         <v>47.960396039603964</v>
       </c>
       <c r="G18" s="22">
-        <v>0.005093935191022569</v>
+        <v>0.005341654326211128</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19182,7 +18626,7 @@
         <v>42.49142857142857</v>
       </c>
       <c r="G19" s="22">
-        <v>0.00441306266548985</v>
+        <v>0.004627670827163106</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19203,7 +18647,7 @@
         <v>67.98823529411764</v>
       </c>
       <c r="G20" s="22">
-        <v>0.002143487580380784</v>
+        <v>0.0022477258303363655</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19224,7 +18668,7 @@
         <v>77.0</v>
       </c>
       <c r="G21" s="22">
-        <v>0.00088261253309797</v>
+        <v>0.0009255341654326212</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
